--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.96</v>
+        <v>4.63</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N13" t="n">
         <v>4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.46</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
         <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>3.06</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>2.24</v>
       </c>
       <c r="O25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.08</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>3.29</v>
+        <v>3.68</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,55 +3753,55 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.82</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.68</v>
+        <v>3.29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.31</v>
+        <v>1.82</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N36" t="n">
-        <v>2.94</v>
+        <v>4.13</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="N42" t="n">
-        <v>6.15</v>
+        <v>7.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI43"/>
+  <dimension ref="A1:AI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.63</v>
+        <v>3.84</v>
       </c>
       <c r="N11" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.84</v>
+        <v>4.63</v>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>1.46</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="N14" t="n">
-        <v>6.06</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.46</v>
+        <v>6.06</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46077.6875</v>
+        <v>46077.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,80 +2797,80 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46077.69791666666</v>
+        <v>46077.6875</v>
       </c>
     </row>
     <row r="21">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
-        <v>6.9</v>
+        <v>5.55</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.77</v>
+        <v>2.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.68</v>
+        <v>2.94</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N30" t="n">
-        <v>3.29</v>
+        <v>4.13</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O31" t="n">
-        <v>4.16</v>
+        <v>2.5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
         <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>3.68</v>
       </c>
       <c r="O32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>5.5</v>
+        <v>2.08</v>
       </c>
       <c r="O33" t="n">
-        <v>2.07</v>
+        <v>4.16</v>
       </c>
       <c r="P33" t="n">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.7</v>
+        <v>2.76</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T33" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U33" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>5.55</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH33" t="n">
-        <v>2.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="O34" t="n">
-        <v>3.97</v>
+        <v>3.72</v>
       </c>
       <c r="P34" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="R34" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="T34" t="n">
-        <v>3.24</v>
+        <v>3.01</v>
       </c>
       <c r="U34" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="V34" t="n">
-        <v>8.800000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.32</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="N36" t="n">
-        <v>4.13</v>
+        <v>5.37</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,80 +4820,80 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>46077.70833333334</v>
+        <v>46077.69791666666</v>
       </c>
     </row>
     <row r="38">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5259,27 +5259,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5369,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="AI41" s="3" t="n">
-        <v>46077.875</v>
+        <v>46077.70833333334</v>
       </c>
     </row>
     <row r="42">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="N43" t="n">
-        <v>6.15</v>
+        <v>7.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5607,6 +5607,125 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
+        <v>46077.875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3" t="n">
         <v>46077.875</v>
       </c>
     </row>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.1</v>
+        <v>2.94</v>
       </c>
       <c r="O26" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>4.42</v>
+        <v>5.37</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="O31" t="n">
-        <v>2.5</v>
+        <v>3.72</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
         <v>1.26</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,77 +4225,77 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.68</v>
+        <v>2.08</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.08</v>
+        <v>3.68</v>
       </c>
       <c r="O33" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O34" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="P34" t="n">
         <v>2.03</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="T34" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="U34" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="N36" t="n">
-        <v>5.37</v>
+        <v>4.42</v>
       </c>
       <c r="O36" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="M37" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S37" t="n">
         <v>2.7</v>
       </c>
-      <c r="O37" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.47</v>
-      </c>
       <c r="T37" t="n">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V37" t="n">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.8</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.46</v>
+        <v>6.06</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
-        <v>5.25</v>
+        <v>3.82</v>
       </c>
       <c r="N15" t="n">
-        <v>6.06</v>
+        <v>4.38</v>
       </c>
       <c r="O15" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V15" t="n">
         <v>5.75</v>
       </c>
-      <c r="R15" t="n">
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.19</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z15" t="n">
-        <v>5.3</v>
+        <v>3.82</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.24</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.82</v>
+        <v>4.63</v>
       </c>
       <c r="N16" t="n">
-        <v>4.38</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>4.13</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>2.08</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>4.42</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.06</v>
+        <v>2.31</v>
       </c>
       <c r="M25" t="n">
         <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.31</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.15</v>
+        <v>1.96</v>
       </c>
       <c r="M28" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>3.68</v>
       </c>
       <c r="O28" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>5.37</v>
+        <v>2.18</v>
       </c>
       <c r="O29" t="n">
-        <v>2.19</v>
+        <v>3.72</v>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>2.99</v>
       </c>
       <c r="R29" t="n">
         <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W29" t="n">
         <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.21</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N31" t="n">
-        <v>2.18</v>
+        <v>5.37</v>
       </c>
       <c r="O31" t="n">
-        <v>3.72</v>
+        <v>2.19</v>
       </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.99</v>
+        <v>4.5</v>
       </c>
       <c r="R31" t="n">
         <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>2.21</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,77 +4225,77 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.08</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>4.16</v>
+        <v>2.8</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.4</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V32" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.96</v>
+        <v>3.06</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.68</v>
+        <v>2.24</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="M35" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.13</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.8</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N42" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
-        <v>3.86</v>
+        <v>4.36</v>
       </c>
       <c r="N44" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="N12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="N13" t="n">
-        <v>6.06</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.7</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.38</v>
+        <v>1.46</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>4.63</v>
+        <v>3.82</v>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>4.38</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>4.13</v>
+        <v>5.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.42</v>
+        <v>2.18</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.31</v>
+        <v>3.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>5.37</v>
       </c>
       <c r="O26" t="n">
-        <v>3.97</v>
+        <v>2.19</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.47</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.15</v>
+        <v>3.71</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>2.21</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>5.55</v>
+        <v>6.9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
         <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="N28" t="n">
-        <v>3.68</v>
+        <v>4.42</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3878,67 +3878,67 @@
         <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="O29" t="n">
-        <v>3.72</v>
+        <v>4.16</v>
       </c>
       <c r="P29" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>2.31</v>
       </c>
       <c r="M31" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>5.37</v>
+        <v>2.94</v>
       </c>
       <c r="O31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>3.68</v>
       </c>
       <c r="O32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.1</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1</v>
+        <v>3.29</v>
       </c>
       <c r="O34" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N35" t="n">
-        <v>3.29</v>
+        <v>4.13</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N36" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M42" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N43" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.84</v>
+        <v>5.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.82</v>
+        <v>6.06</v>
       </c>
       <c r="O11" t="n">
-        <v>4.43</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>5.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>3.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>4.63</v>
+        <v>3.82</v>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>4.38</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.96</v>
+        <v>4.63</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="M14" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>6.06</v>
+        <v>1.46</v>
       </c>
       <c r="O14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N15" t="n">
         <v>4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.46</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="N16" t="n">
-        <v>4.38</v>
+        <v>1.82</v>
       </c>
       <c r="O16" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.3</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>2.18</v>
+        <v>5.37</v>
       </c>
       <c r="O24" t="n">
-        <v>3.72</v>
+        <v>2.19</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.99</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
         <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>2.21</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
         <v>3.1</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O25" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="P25" t="n">
         <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="U25" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.06</v>
       </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>5.37</v>
+        <v>3.68</v>
       </c>
       <c r="O26" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AB26" t="n">
         <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.88</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.89</v>
       </c>
       <c r="AB27" t="n">
         <v>1.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="M28" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.42</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,70 +3872,70 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O29" t="n">
-        <v>4.16</v>
+        <v>3.78</v>
       </c>
       <c r="P29" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R29" t="n">
         <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
         <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
         <v>1.3</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.06</v>
+        <v>1.88</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2.24</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB30" t="n">
         <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>2.94</v>
+        <v>2.08</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="N32" t="n">
-        <v>3.68</v>
+        <v>4.13</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="M34" t="n">
         <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>3.29</v>
+        <v>2.94</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="M35" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="N35" t="n">
-        <v>4.13</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="M36" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>4.6</v>
+        <v>3.29</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>4.42</v>
       </c>
       <c r="O37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>3.45</v>
       </c>
       <c r="M11" t="n">
-        <v>5.25</v>
+        <v>3.84</v>
       </c>
       <c r="N11" t="n">
-        <v>6.06</v>
+        <v>1.82</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>4.43</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.24</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>4.38</v>
+        <v>1.46</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>4.63</v>
+        <v>5.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>6.06</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N14" t="n">
         <v>4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.46</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.7</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.84</v>
+        <v>4.63</v>
       </c>
       <c r="N16" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>4.13</v>
       </c>
       <c r="O21" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>3.06</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>5.37</v>
+        <v>2.24</v>
       </c>
       <c r="O24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.18</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.72</v>
+        <v>2.07</v>
       </c>
       <c r="P25" t="n">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.99</v>
+        <v>4.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.37</v>
       </c>
-      <c r="V25" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.68</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
         <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.24</v>
+        <v>3.29</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>2.08</v>
       </c>
       <c r="O28" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.8</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC29" t="n">
         <v>3.3</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>3.97</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.7</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AA30" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>3.68</v>
       </c>
       <c r="O31" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,77 +4225,77 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>4.13</v>
+        <v>2.1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="O33" t="n">
-        <v>3.97</v>
+        <v>3.72</v>
       </c>
       <c r="P33" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="R33" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="T33" t="n">
-        <v>3.24</v>
+        <v>3.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>8.800000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.32</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M35" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>5.37</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="M37" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>4.42</v>
+        <v>2.94</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N42" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -175,33 +175,33 @@
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
+    <t>Saudi Arabia Professional League</t>
+  </si>
+  <si>
     <t>Netherlands Eerste Divisie</t>
   </si>
   <si>
     <t>Belgium First Division B</t>
   </si>
   <si>
-    <t>Saudi Arabia Professional League</t>
-  </si>
-  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>England EFL League One</t>
+  </si>
+  <si>
     <t>England Championship</t>
   </si>
   <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>England EFL League Two</t>
   </si>
   <si>
-    <t>England EFL League One</t>
-  </si>
-  <si>
     <t>Northern Ireland NIFL Premiership</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -238,34 +238,55 @@
     <t>Al Ahli</t>
   </si>
   <si>
+    <t>Al Hazm</t>
+  </si>
+  <si>
+    <t>Cambuur</t>
+  </si>
+  <si>
+    <t>Al Khaleej</t>
+  </si>
+  <si>
     <t>Willem II</t>
   </si>
   <si>
-    <t>Cambuur</t>
+    <t>Al Taawon</t>
   </si>
   <si>
     <t>KAA Gent II</t>
   </si>
   <si>
-    <t>Al Taawon</t>
-  </si>
-  <si>
-    <t>Al Hazm</t>
-  </si>
-  <si>
-    <t>Al Khaleej</t>
+    <t>Ceramica Cleopatra</t>
+  </si>
+  <si>
+    <t>Masr</t>
+  </si>
+  <si>
+    <t>Haras El Hodood</t>
   </si>
   <si>
     <t>Ghazl El Mehalla</t>
   </si>
   <si>
-    <t>Ceramica Cleopatra</t>
-  </si>
-  <si>
-    <t>Masr</t>
-  </si>
-  <si>
-    <t>Haras El Hodood</t>
+    <t>Burton Albion</t>
+  </si>
+  <si>
+    <t>West Bromwich Albion</t>
+  </si>
+  <si>
+    <t>Dundee United</t>
+  </si>
+  <si>
+    <t>Doncaster Rovers</t>
+  </si>
+  <si>
+    <t>Bradford City</t>
+  </si>
+  <si>
+    <t>Swansea City</t>
+  </si>
+  <si>
+    <t>Northampton Town</t>
   </si>
   <si>
     <t>Wrexham</t>
@@ -274,49 +295,31 @@
     <t>Salford City</t>
   </si>
   <si>
-    <t>Northampton Town</t>
+    <t>Middlesbrough</t>
+  </si>
+  <si>
+    <t>Larne</t>
+  </si>
+  <si>
+    <t>Accrington Stanley</t>
+  </si>
+  <si>
+    <t>Cliftonville</t>
+  </si>
+  <si>
+    <t>Watford</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Ballymena United</t>
   </si>
   <si>
     <t>Hull City</t>
   </si>
   <si>
-    <t>Middlesbrough</t>
-  </si>
-  <si>
-    <t>Watford</t>
-  </si>
-  <si>
-    <t>Bradford City</t>
-  </si>
-  <si>
-    <t>West Bromwich Albion</t>
-  </si>
-  <si>
-    <t>Swansea City</t>
-  </si>
-  <si>
-    <t>Larne</t>
-  </si>
-  <si>
-    <t>Ballymena United</t>
-  </si>
-  <si>
-    <t>Burton Albion</t>
-  </si>
-  <si>
-    <t>Accrington Stanley</t>
-  </si>
-  <si>
-    <t>Dundee United</t>
-  </si>
-  <si>
-    <t>Doncaster Rovers</t>
-  </si>
-  <si>
-    <t>Cliftonville</t>
-  </si>
-  <si>
-    <t>Blackburn Rovers</t>
+    <t>Newcastle United</t>
   </si>
   <si>
     <t>Bayer Leverkusen</t>
@@ -328,18 +331,15 @@
     <t>Southampton</t>
   </si>
   <si>
-    <t>Newcastle United</t>
+    <t>Bahia</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
   </si>
   <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Flamengo</t>
-  </si>
-  <si>
-    <t>Bahia</t>
-  </si>
-  <si>
     <t>Turan</t>
   </si>
   <si>
@@ -367,34 +367,55 @@
     <t>Shabab Al Ordon</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Eindhoven</t>
+  </si>
+  <si>
+    <t>Al Kholood</t>
+  </si>
+  <si>
     <t>ADO Den Haag</t>
   </si>
   <si>
-    <t>Eindhoven</t>
+    <t>Al Hilal</t>
   </si>
   <si>
     <t>Olympic Charleroi</t>
   </si>
   <si>
-    <t>Al Hilal</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Al Kholood</t>
+    <t>Ismaily SC</t>
+  </si>
+  <si>
+    <t>Zamalek</t>
+  </si>
+  <si>
+    <t>ENPPI</t>
   </si>
   <si>
     <t>Pyramids FC</t>
   </si>
   <si>
-    <t>Ismaily SC</t>
-  </si>
-  <si>
-    <t>Zamalek</t>
-  </si>
-  <si>
-    <t>ENPPI</t>
+    <t>Stockport County</t>
+  </si>
+  <si>
+    <t>Charlton Athletic</t>
+  </si>
+  <si>
+    <t>Aberdeen</t>
+  </si>
+  <si>
+    <t>Luton Town</t>
+  </si>
+  <si>
+    <t>Rotherham United</t>
+  </si>
+  <si>
+    <t>Preston North End</t>
+  </si>
+  <si>
+    <t>Port Vale</t>
   </si>
   <si>
     <t>Portsmouth</t>
@@ -403,49 +424,31 @@
     <t>Shrewsbury Town</t>
   </si>
   <si>
-    <t>Port Vale</t>
+    <t>Leicester City</t>
+  </si>
+  <si>
+    <t>Linfield</t>
+  </si>
+  <si>
+    <t>Barnet</t>
+  </si>
+  <si>
+    <t>Glentoran</t>
+  </si>
+  <si>
+    <t>Ipswich Town</t>
+  </si>
+  <si>
+    <t>Bristol City</t>
+  </si>
+  <si>
+    <t>Glenavon</t>
   </si>
   <si>
     <t>Derby County</t>
   </si>
   <si>
-    <t>Leicester City</t>
-  </si>
-  <si>
-    <t>Ipswich Town</t>
-  </si>
-  <si>
-    <t>Rotherham United</t>
-  </si>
-  <si>
-    <t>Charlton Athletic</t>
-  </si>
-  <si>
-    <t>Preston North End</t>
-  </si>
-  <si>
-    <t>Linfield</t>
-  </si>
-  <si>
-    <t>Glenavon</t>
-  </si>
-  <si>
-    <t>Stockport County</t>
-  </si>
-  <si>
-    <t>Barnet</t>
-  </si>
-  <si>
-    <t>Aberdeen</t>
-  </si>
-  <si>
-    <t>Luton Town</t>
-  </si>
-  <si>
-    <t>Glentoran</t>
-  </si>
-  <si>
-    <t>Bristol City</t>
+    <t>Qarabağ</t>
   </si>
   <si>
     <t>Olympiakos Piraeus</t>
@@ -457,16 +460,13 @@
     <t>Queens Park Rangers</t>
   </si>
   <si>
-    <t>Qarabağ</t>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
   </si>
   <si>
     <t>Vitória</t>
-  </si>
-  <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Chapecoense</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1516,13 +1516,13 @@
         <v>151</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1623,13 +1623,13 @@
         <v>151</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>151</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
@@ -1944,73 +1944,73 @@
         <v>151</v>
       </c>
       <c r="L11">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="M11">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="O11">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3">
         <v>46077.66666666666</v>
@@ -2024,7 +2024,7 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>63</v>
@@ -2131,7 +2131,7 @@
         <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
         <v>63</v>
@@ -2158,73 +2158,73 @@
         <v>151</v>
       </c>
       <c r="L13">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M13">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="N13">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3">
         <v>46077.66666666666</v>
@@ -2238,7 +2238,7 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
         <v>63</v>
@@ -2265,73 +2265,73 @@
         <v>151</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="M14">
-        <v>4.63</v>
+        <v>3.84</v>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3">
         <v>46077.66666666666</v>
@@ -2345,7 +2345,7 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>63</v>
@@ -2372,13 +2372,13 @@
         <v>151</v>
       </c>
       <c r="L15">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="N15">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -2479,73 +2479,73 @@
         <v>151</v>
       </c>
       <c r="L16">
+        <v>1.73</v>
+      </c>
+      <c r="M16">
+        <v>3.82</v>
+      </c>
+      <c r="N16">
+        <v>4.38</v>
+      </c>
+      <c r="O16">
+        <v>2.3</v>
+      </c>
+      <c r="P16">
+        <v>2.3</v>
+      </c>
+      <c r="Q16">
+        <v>4</v>
+      </c>
+      <c r="R16">
+        <v>1.31</v>
+      </c>
+      <c r="S16">
+        <v>3.02</v>
+      </c>
+      <c r="T16">
+        <v>2.47</v>
+      </c>
+      <c r="U16">
+        <v>1.45</v>
+      </c>
+      <c r="V16">
+        <v>5.75</v>
+      </c>
+      <c r="W16">
+        <v>1.07</v>
+      </c>
+      <c r="X16">
+        <v>1.04</v>
+      </c>
+      <c r="Y16">
+        <v>1.19</v>
+      </c>
+      <c r="Z16">
+        <v>3.82</v>
+      </c>
+      <c r="AA16">
         <v>1.7</v>
       </c>
-      <c r="M16">
-        <v>3.96</v>
-      </c>
-      <c r="N16">
-        <v>4</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI16" s="3">
         <v>46077.66666666666</v>
@@ -3014,13 +3014,13 @@
         <v>151</v>
       </c>
       <c r="L21">
-        <v>1.96</v>
+        <v>3.65</v>
       </c>
       <c r="M21">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N21">
-        <v>3.68</v>
+        <v>1.92</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -3059,10 +3059,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3121,73 +3121,73 @@
         <v>151</v>
       </c>
       <c r="L22">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="M22">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="N22">
-        <v>5.5</v>
+        <v>4.42</v>
       </c>
       <c r="O22">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB22">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC22">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3">
         <v>46077.69791666666</v>
@@ -3228,73 +3228,73 @@
         <v>151</v>
       </c>
       <c r="L23">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M23">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" s="3">
         <v>46077.69791666666</v>
@@ -3335,73 +3335,73 @@
         <v>151</v>
       </c>
       <c r="L24">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M24">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N24">
-        <v>3.29</v>
+        <v>2.18</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA24">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB24">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3">
         <v>46077.69791666666</v>
@@ -3439,76 +3439,76 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L25">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M25">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="N25">
-        <v>4.6</v>
+        <v>5.37</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA25">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB25">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI25" s="3">
         <v>46077.69791666666</v>
@@ -3522,7 +3522,7 @@
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
         <v>63</v>
@@ -3549,13 +3549,13 @@
         <v>151</v>
       </c>
       <c r="L26">
-        <v>3.06</v>
+        <v>1.82</v>
       </c>
       <c r="M26">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N26">
-        <v>2.24</v>
+        <v>4.13</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
         <v>63</v>
@@ -3653,76 +3653,76 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L27">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="M27">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N27">
-        <v>5.37</v>
+        <v>2.6</v>
       </c>
       <c r="O27">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3">
         <v>46077.69791666666</v>
@@ -3736,7 +3736,7 @@
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
         <v>63</v>
@@ -3763,13 +3763,13 @@
         <v>151</v>
       </c>
       <c r="L28">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="M28">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="N28">
-        <v>4.42</v>
+        <v>3.68</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -3808,10 +3808,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB28">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
         <v>63</v>
@@ -3870,73 +3870,73 @@
         <v>151</v>
       </c>
       <c r="L29">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="M29">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="N29">
-        <v>4.13</v>
+        <v>5.5</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AB29">
+        <v>2.1</v>
+      </c>
+      <c r="AC29">
+        <v>2.66</v>
+      </c>
+      <c r="AD29">
+        <v>1.37</v>
+      </c>
+      <c r="AE29">
         <v>1.78</v>
       </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI29" s="3">
         <v>46077.69791666666</v>
@@ -3950,7 +3950,7 @@
         <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
         <v>63</v>
@@ -3974,76 +3974,76 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L30">
-        <v>3.15</v>
+        <v>1.66</v>
       </c>
       <c r="M30">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="N30">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="O30">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3">
         <v>46077.69791666666</v>
@@ -4057,7 +4057,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
         <v>63</v>
@@ -4081,76 +4081,76 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L31">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="M31">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="N31">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="O31">
-        <v>2.5</v>
+        <v>3.97</v>
       </c>
       <c r="P31">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q31">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="R31">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S31">
+        <v>2.47</v>
+      </c>
+      <c r="T31">
+        <v>3.24</v>
+      </c>
+      <c r="U31">
+        <v>1.28</v>
+      </c>
+      <c r="V31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W31">
+        <v>1.03</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.36</v>
+      </c>
+      <c r="Z31">
         <v>2.7</v>
       </c>
-      <c r="T31">
-        <v>2.75</v>
-      </c>
-      <c r="U31">
-        <v>1.42</v>
-      </c>
-      <c r="V31">
-        <v>6.9</v>
-      </c>
-      <c r="W31">
-        <v>1.07</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>1.25</v>
-      </c>
-      <c r="Z31">
-        <v>3.35</v>
-      </c>
       <c r="AA31">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AB31">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC31">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD31">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AE31">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF31">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AG31">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH31">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AI31" s="3">
         <v>46077.69791666666</v>
@@ -4164,7 +4164,7 @@
         <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
         <v>63</v>
@@ -4191,73 +4191,73 @@
         <v>151</v>
       </c>
       <c r="L32">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="M32">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N32">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3">
         <v>46077.69791666666</v>
@@ -4271,7 +4271,7 @@
         <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
         <v>63</v>
@@ -4295,73 +4295,73 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M33">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N33">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O33">
-        <v>4.16</v>
+        <v>3.78</v>
       </c>
       <c r="P33">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="Q33">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R33">
         <v>1.4</v>
       </c>
       <c r="S33">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="T33">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U33">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V33">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA33">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB33">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
         <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AF33">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG33">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH33">
         <v>1.3</v>
@@ -4378,7 +4378,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
         <v>63</v>
@@ -4405,73 +4405,73 @@
         <v>151</v>
       </c>
       <c r="L34">
-        <v>2.35</v>
+        <v>3.06</v>
       </c>
       <c r="M34">
         <v>3.4</v>
       </c>
       <c r="N34">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="O34">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA34">
         <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3">
         <v>46077.69791666666</v>
@@ -4485,7 +4485,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
         <v>63</v>
@@ -4512,73 +4512,73 @@
         <v>151</v>
       </c>
       <c r="L35">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M35">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N35">
-        <v>2.18</v>
+        <v>2.94</v>
       </c>
       <c r="O35">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB35">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3">
         <v>46077.69791666666</v>
@@ -4592,7 +4592,7 @@
         <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D36" t="s">
         <v>63</v>
@@ -4616,76 +4616,76 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L36">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="M36">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="O36">
-        <v>3.78</v>
+        <v>2.5</v>
       </c>
       <c r="P36">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q36">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="R36">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S36">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T36">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="U36">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V36">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA36">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AB36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
         <v>3.2</v>
       </c>
       <c r="AD36">
+        <v>1.26</v>
+      </c>
+      <c r="AE36">
+        <v>1.75</v>
+      </c>
+      <c r="AF36">
+        <v>1.95</v>
+      </c>
+      <c r="AG36">
         <v>1.25</v>
       </c>
-      <c r="AE36">
+      <c r="AH36">
         <v>1.77</v>
-      </c>
-      <c r="AF36">
-        <v>2</v>
-      </c>
-      <c r="AG36">
-        <v>1.33</v>
-      </c>
-      <c r="AH36">
-        <v>1.3</v>
       </c>
       <c r="AI36" s="3">
         <v>46077.69791666666</v>
@@ -4699,7 +4699,7 @@
         <v>44</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
         <v>63</v>
@@ -4726,13 +4726,13 @@
         <v>151</v>
       </c>
       <c r="L37">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="M37">
         <v>3.4</v>
       </c>
       <c r="N37">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="O37">
         <v>0</v>
@@ -4771,10 +4771,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -4833,13 +4833,13 @@
         <v>151</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -4940,13 +4940,13 @@
         <v>151</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -4985,10 +4985,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -5020,7 +5020,7 @@
         <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D40" t="s">
         <v>63</v>
@@ -5047,13 +5047,13 @@
         <v>151</v>
       </c>
       <c r="L40">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="M40">
-        <v>3.96</v>
+        <v>7.5</v>
       </c>
       <c r="N40">
-        <v>4.51</v>
+        <v>10.6</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -5092,16 +5092,16 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -5127,7 +5127,7 @@
         <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D41" t="s">
         <v>63</v>
@@ -5154,13 +5154,13 @@
         <v>151</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -5258,16 +5258,16 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L42">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M42">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N42">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -5306,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB42">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -5472,16 +5472,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L44">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M44">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N44">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -5520,10 +5520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB44">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC44">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.65</v>
+        <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.45</v>
+        <v>4.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>7.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>4.62</v>
+        <v>1.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="N11" t="n">
-        <v>1.82</v>
+        <v>4.38</v>
       </c>
       <c r="O11" t="n">
-        <v>4.43</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V11" t="n">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.63</v>
+        <v>3.96</v>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="N13" t="n">
-        <v>4.38</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.3</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="M14" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>6.06</v>
+        <v>1.46</v>
       </c>
       <c r="O14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.96</v>
+        <v>4.63</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.8</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.46</v>
+        <v>6.06</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5.37</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.19</v>
+        <v>3.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.5</v>
+        <v>2.77</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
         <v>2.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.71</v>
+        <v>3.2</v>
       </c>
       <c r="AD22" t="n">
         <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.09</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.21</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>3.68</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.65</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>4.13</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="N28" t="n">
-        <v>5.5</v>
+        <v>4.42</v>
       </c>
       <c r="O28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
         <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,74 +4106,74 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
         <v>3.1</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O31" t="n">
-        <v>3.78</v>
+        <v>4.16</v>
       </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="R31" t="n">
         <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD31" t="n">
         <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="n">
         <v>1.3</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.06</v>
+        <v>2.35</v>
       </c>
       <c r="M32" t="n">
         <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.24</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA32" t="n">
         <v>1.88</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M33" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>4.42</v>
+        <v>5.37</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>4.13</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.35</v>
+        <v>3.65</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>3.15</v>
+        <v>1.92</v>
       </c>
       <c r="O35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.15</v>
+        <v>2.31</v>
       </c>
       <c r="M38" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="O38" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O39" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M45" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N46" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.9</v>
+        <v>7.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>4.62</v>
+        <v>1.45</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.65</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.45</v>
+        <v>4.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.82</v>
+        <v>5.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4.38</v>
+        <v>6.06</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>3.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="U11" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.82</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>3.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="N14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
-        <v>4.63</v>
+        <v>3.82</v>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>4.38</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>5.25</v>
+        <v>3.84</v>
       </c>
       <c r="N16" t="n">
-        <v>6.06</v>
+        <v>1.82</v>
       </c>
       <c r="O16" t="n">
-        <v>1.75</v>
+        <v>4.43</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.88</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.24</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.39</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.1</v>
+        <v>1.56</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.78</v>
+        <v>2.07</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.77</v>
+        <v>4.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>2.93</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="V22" t="n">
-        <v>7.1</v>
+        <v>5.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.03</v>
+        <v>1.73</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>2.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.97</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
         <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>3.68</v>
+        <v>5.37</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
         <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>8</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>4.93</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>1.36</v>
       </c>
       <c r="O25" t="n">
-        <v>2.07</v>
+        <v>7.66</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.7</v>
+        <v>1.83</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="U25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.45</v>
       </c>
-      <c r="V25" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.33</v>
+        <v>1.01</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="O31" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="M32" t="n">
         <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>5.37</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>2.19</v>
+        <v>2.8</v>
       </c>
       <c r="P33" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="T33" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
         <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.71</v>
+        <v>3.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="M34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z34" t="n">
         <v>3.1</v>
       </c>
-      <c r="N34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="O36" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="M37" t="n">
-        <v>4.93</v>
+        <v>2.6</v>
       </c>
       <c r="N37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.36</v>
       </c>
-      <c r="O37" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V37" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z37" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.06</v>
+        <v>1.96</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.24</v>
+        <v>3.68</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.86</v>
+        <v>1.27</v>
       </c>
       <c r="M40" t="n">
-        <v>3.99</v>
+        <v>7.5</v>
       </c>
       <c r="N40" t="n">
-        <v>4.41</v>
+        <v>10.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>10.8</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>13.1</v>
+        <v>4.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>7.5</v>
+        <v>3.99</v>
       </c>
       <c r="N42" t="n">
-        <v>10.6</v>
+        <v>4.41</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="M43" t="n">
-        <v>3.96</v>
+        <v>10.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4.51</v>
+        <v>13.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="M44" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="O44" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="P44" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.5</v>
+        <v>5.95</v>
       </c>
       <c r="R44" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="T44" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U44" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>6.05</v>
+        <v>6.35</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.875</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N45" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="M46" t="n">
-        <v>3.86</v>
+        <v>4.36</v>
       </c>
       <c r="N46" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.65</v>
+        <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.45</v>
+        <v>4.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>7.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>4.62</v>
+        <v>1.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>5.25</v>
+        <v>4.63</v>
       </c>
       <c r="N11" t="n">
-        <v>6.06</v>
+        <v>1.44</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>1.46</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.8</v>
+        <v>1.73</v>
       </c>
       <c r="M13" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>4</v>
       </c>
-      <c r="N13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>4.63</v>
+        <v>3.96</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="N15" t="n">
-        <v>4.38</v>
+        <v>1.82</v>
       </c>
       <c r="O15" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.3</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>1.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.84</v>
+        <v>5.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.82</v>
+        <v>6.06</v>
       </c>
       <c r="O16" t="n">
-        <v>4.43</v>
+        <v>1.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>5.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>3.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.94</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>3.24</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2926,67 +2926,67 @@
         <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="O21" t="n">
-        <v>3.72</v>
+        <v>4.16</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>5.55</v>
+        <v>7.1</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.33</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>4.93</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>7.66</v>
       </c>
       <c r="P23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="AF23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.37</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.19</v>
+        <v>3.78</v>
       </c>
       <c r="P24" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.5</v>
+        <v>2.77</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
         <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.71</v>
+        <v>3.2</v>
       </c>
       <c r="AD24" t="n">
         <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.09</v>
+        <v>1.77</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.21</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>8</v>
+        <v>2.35</v>
       </c>
       <c r="M25" t="n">
-        <v>4.93</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.36</v>
+        <v>3.15</v>
       </c>
       <c r="O25" t="n">
-        <v>7.66</v>
+        <v>2.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
         <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>3.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3.62</v>
+        <v>2.6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.13</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="M28" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.42</v>
+        <v>2.94</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.29</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.65</v>
+        <v>1.96</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>1.92</v>
+        <v>3.68</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.31</v>
+        <v>3.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>1.92</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
         <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="O33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1</v>
+        <v>5.37</v>
       </c>
       <c r="O34" t="n">
-        <v>3.78</v>
+        <v>2.19</v>
       </c>
       <c r="P34" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T34" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.35</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA34" t="n">
         <v>2.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="AD34" t="n">
         <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.77</v>
+        <v>2.09</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>2.08</v>
+        <v>4.42</v>
       </c>
       <c r="O35" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="M37" t="n">
-        <v>2.6</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>4.13</v>
       </c>
       <c r="O37" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V39" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC39" t="n">
         <v>3.5</v>
       </c>
-      <c r="N39" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="M40" t="n">
-        <v>7.5</v>
+        <v>10.8</v>
       </c>
       <c r="N40" t="n">
-        <v>10.6</v>
+        <v>13.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="M41" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="N41" t="n">
-        <v>4.51</v>
+        <v>4.41</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="M42" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="N42" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="M43" t="n">
-        <v>10.8</v>
+        <v>7.5</v>
       </c>
       <c r="N43" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5589,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="N44" t="n">
-        <v>6.15</v>
+        <v>7.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="P44" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S44" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="T44" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U44" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V44" t="n">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.875</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M45" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4.36</v>
+        <v>3.86</v>
       </c>
       <c r="N46" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="O46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>1.73</v>
       </c>
       <c r="M11" t="n">
-        <v>4.63</v>
+        <v>3.82</v>
       </c>
       <c r="N11" t="n">
-        <v>1.44</v>
+        <v>4.38</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="N12" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.73</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.82</v>
+        <v>4.63</v>
       </c>
       <c r="N13" t="n">
-        <v>4.38</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.7</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="N15" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>6.06</v>
+        <v>1.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,74 +2916,74 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4.16</v>
+        <v>3.78</v>
       </c>
       <c r="P21" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
         <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
         <v>1.3</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>2.55</v>
       </c>
       <c r="M23" t="n">
-        <v>4.93</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="O24" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.35</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>5.55</v>
+        <v>6.9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.15</v>
       </c>
-      <c r="M27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O27" t="n">
-        <v>3.97</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="T27" t="n">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.32</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.31</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>2.94</v>
+        <v>5.37</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.55</v>
+        <v>1.56</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
       <c r="M30" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N31" t="n">
-        <v>3.68</v>
+        <v>2.3</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.65</v>
+        <v>1.96</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.92</v>
+        <v>3.68</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.13</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>4.93</v>
       </c>
       <c r="N33" t="n">
-        <v>3.29</v>
+        <v>1.36</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>7.66</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>5.37</v>
+        <v>3.29</v>
       </c>
       <c r="O34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>4.05</v>
       </c>
       <c r="N35" t="n">
-        <v>4.42</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.06</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="N36" t="n">
-        <v>2.24</v>
+        <v>4.42</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.82</v>
+        <v>3.65</v>
       </c>
       <c r="M37" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>4.13</v>
+        <v>1.92</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>4.13</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5068,67 +5068,67 @@
         <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="O39" t="n">
-        <v>3.72</v>
+        <v>4.16</v>
       </c>
       <c r="P39" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="T39" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U39" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="M40" t="n">
-        <v>10.8</v>
+        <v>3.96</v>
       </c>
       <c r="N40" t="n">
-        <v>13.1</v>
+        <v>4.51</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.86</v>
+        <v>1.18</v>
       </c>
       <c r="M41" t="n">
-        <v>3.99</v>
+        <v>10.8</v>
       </c>
       <c r="N41" t="n">
-        <v>4.41</v>
+        <v>13.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="N42" t="n">
-        <v>4.51</v>
+        <v>4.41</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="M44" t="n">
-        <v>4.36</v>
+        <v>3.86</v>
       </c>
       <c r="N44" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="O44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.875</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="N45" t="n">
-        <v>6.15</v>
+        <v>7.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="P45" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S45" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V45" t="n">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M46" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.84</v>
+        <v>5.25</v>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>6.06</v>
       </c>
       <c r="O12" t="n">
-        <v>4.43</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>5.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>3.88</v>
       </c>
       <c r="T12" t="n">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.94</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>3.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.63</v>
+        <v>3.96</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="M14" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>6.06</v>
+        <v>1.46</v>
       </c>
       <c r="O14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.96</v>
+        <v>4.63</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="N16" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>4.13</v>
       </c>
       <c r="O21" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>2.94</v>
       </c>
       <c r="O22" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.55</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O24" t="n">
         <v>3.4</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="M25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N25" t="n">
         <v>2.6</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O25" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.35</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>4.93</v>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>1.36</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>7.66</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.56</v>
+        <v>3.15</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="N29" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>2.07</v>
+        <v>3.97</v>
       </c>
       <c r="P29" t="n">
-        <v>2.48</v>
+        <v>1.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.7</v>
+        <v>2.98</v>
       </c>
       <c r="R29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.32</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.33</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
         <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.8</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>1.36</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.96</v>
+        <v>3.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>3.68</v>
+        <v>1.92</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>8</v>
+        <v>3.06</v>
       </c>
       <c r="M33" t="n">
-        <v>4.93</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>1.36</v>
+        <v>2.24</v>
       </c>
       <c r="O33" t="n">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>3.29</v>
+        <v>4.42</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AB35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF35" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="M36" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>4.42</v>
+        <v>2.1</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF36" t="n">
         <v>2</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>1.92</v>
+        <v>3.15</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="M38" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.13</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.08</v>
+        <v>3.68</v>
       </c>
       <c r="O39" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="M40" t="n">
-        <v>3.96</v>
+        <v>10.8</v>
       </c>
       <c r="N40" t="n">
-        <v>4.51</v>
+        <v>13.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>10.8</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>13.1</v>
+        <v>4.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>1.27</v>
       </c>
       <c r="M42" t="n">
-        <v>3.99</v>
+        <v>7.5</v>
       </c>
       <c r="N42" t="n">
-        <v>4.41</v>
+        <v>10.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>7.5</v>
+        <v>3.99</v>
       </c>
       <c r="N43" t="n">
-        <v>10.6</v>
+        <v>4.41</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M44" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA44" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N46" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O46" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S46" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V46" t="n">
-        <v>6.35</v>
+        <v>6.65</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="n">
         <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.9</v>
+        <v>7.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>4.62</v>
+        <v>1.45</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.65</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.45</v>
+        <v>4.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.82</v>
+        <v>5.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4.38</v>
+        <v>6.06</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>3.88</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="U11" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.82</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>3.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="N12" t="n">
-        <v>6.06</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.96</v>
+        <v>3.84</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="N16" t="n">
-        <v>1.82</v>
+        <v>4.38</v>
       </c>
       <c r="O16" t="n">
-        <v>4.43</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="T16" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.82</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.31</v>
+        <v>3.65</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2.94</v>
+        <v>1.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
         <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>3.97</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z26" t="n">
         <v>2.7</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AA26" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>4.93</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>4.93</v>
       </c>
       <c r="N28" t="n">
-        <v>5.37</v>
+        <v>1.36</v>
       </c>
       <c r="O28" t="n">
-        <v>2.19</v>
+        <v>7.66</v>
       </c>
       <c r="P28" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>1.83</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>2.84</v>
+        <v>3.08</v>
       </c>
       <c r="T28" t="n">
-        <v>2.95</v>
+        <v>2.58</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="W28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.04</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.71</v>
+        <v>2.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.21</v>
+        <v>1.01</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="M29" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.7</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.47</v>
-      </c>
       <c r="T29" t="n">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
         <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>5.37</v>
       </c>
       <c r="O31" t="n">
-        <v>4.16</v>
+        <v>2.19</v>
       </c>
       <c r="P31" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
         <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.34</v>
+        <v>3.71</v>
       </c>
       <c r="AD31" t="n">
         <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,77 +4225,77 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.06</v>
+        <v>1.82</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N33" t="n">
-        <v>2.24</v>
+        <v>4.13</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="O35" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.1</v>
+        <v>3.68</v>
       </c>
       <c r="O36" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="M37" t="n">
         <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="O37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.68</v>
+        <v>2.08</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="M40" t="n">
-        <v>10.8</v>
+        <v>7.5</v>
       </c>
       <c r="N40" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="M41" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="N41" t="n">
-        <v>4.51</v>
+        <v>4.41</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="M42" t="n">
-        <v>7.5</v>
+        <v>3.96</v>
       </c>
       <c r="N42" t="n">
-        <v>10.6</v>
+        <v>4.51</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>1.18</v>
       </c>
       <c r="M43" t="n">
-        <v>3.99</v>
+        <v>10.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4.41</v>
+        <v>13.1</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="N11" t="n">
-        <v>6.06</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.7</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.84</v>
+        <v>4.63</v>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="N14" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.82</v>
+        <v>5.25</v>
       </c>
       <c r="N16" t="n">
-        <v>4.38</v>
+        <v>6.06</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>3.02</v>
+        <v>3.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.82</v>
+        <v>5.3</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.95</v>
+        <v>3.24</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.65</v>
+        <v>1.96</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>1.92</v>
+        <v>3.68</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>4.93</v>
       </c>
       <c r="N23" t="n">
-        <v>5.5</v>
+        <v>1.36</v>
       </c>
       <c r="O23" t="n">
-        <v>2.07</v>
+        <v>7.66</v>
       </c>
       <c r="P23" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.7</v>
+        <v>1.83</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="T23" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="U23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.45</v>
       </c>
-      <c r="V23" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.33</v>
+        <v>1.01</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
         <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3402,67 +3402,67 @@
         <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
-        <v>3.72</v>
+        <v>4.16</v>
       </c>
       <c r="P25" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>4.42</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>3.06</v>
       </c>
       <c r="M28" t="n">
-        <v>4.93</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.36</v>
+        <v>2.24</v>
       </c>
       <c r="O28" t="n">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V29" t="n">
-        <v>6.9</v>
+        <v>5.55</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
         <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>2.33</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>4.13</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>5.37</v>
+        <v>2.18</v>
       </c>
       <c r="O31" t="n">
-        <v>2.19</v>
+        <v>3.72</v>
       </c>
       <c r="P31" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.5</v>
+        <v>2.99</v>
       </c>
       <c r="R31" t="n">
         <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W31" t="n">
         <v>1.04</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.21</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>2.1</v>
+        <v>5.37</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>2.19</v>
       </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T32" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.35</v>
       </c>
-      <c r="V32" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z32" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA32" t="n">
         <v>2.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="AD32" t="n">
         <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.77</v>
+        <v>2.09</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="M33" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>4.13</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>4.42</v>
+        <v>2.1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA34" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF34" t="n">
         <v>2</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="M35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O35" t="n">
         <v>3.4</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.68</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="M37" t="n">
         <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.66</v>
+        <v>3.15</v>
       </c>
       <c r="M38" t="n">
-        <v>4.05</v>
+        <v>2.6</v>
       </c>
       <c r="N38" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="O39" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="M40" t="n">
-        <v>7.5</v>
+        <v>3.99</v>
       </c>
       <c r="N40" t="n">
-        <v>10.6</v>
+        <v>4.41</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="M42" t="n">
-        <v>3.96</v>
+        <v>10.8</v>
       </c>
       <c r="N42" t="n">
-        <v>4.51</v>
+        <v>13.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,16 +5464,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="M43" t="n">
-        <v>10.8</v>
+        <v>7.5</v>
       </c>
       <c r="N43" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5589,10 +5589,10 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.7</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>4.38</v>
+        <v>1.46</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>4.63</v>
+        <v>3.84</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.84</v>
+        <v>4.63</v>
       </c>
       <c r="N14" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N15" t="n">
         <v>4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.46</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.94</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.68</v>
+        <v>2.94</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>4.93</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.36</v>
-      </c>
-      <c r="O23" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.01</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>4.93</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>1.36</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>7.66</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>3.29</v>
       </c>
       <c r="O25" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3.52</v>
+        <v>2.6</v>
       </c>
       <c r="N27" t="n">
-        <v>4.42</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.56</v>
+        <v>3.1</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="O29" t="n">
-        <v>2.07</v>
+        <v>3.78</v>
       </c>
       <c r="P29" t="n">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.7</v>
+        <v>2.77</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="T29" t="n">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="U29" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>5.55</v>
+        <v>7.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.82</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.18</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
-        <v>3.72</v>
+        <v>2.07</v>
       </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.99</v>
+        <v>4.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T31" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.37</v>
       </c>
-      <c r="V31" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,77 +4225,77 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="N32" t="n">
-        <v>5.37</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P33" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T33" t="n">
         <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.89</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC33" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>2.1</v>
+        <v>5.37</v>
       </c>
       <c r="O34" t="n">
-        <v>3.78</v>
+        <v>2.19</v>
       </c>
       <c r="P34" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T34" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="U34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.35</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA34" t="n">
         <v>2.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="AD34" t="n">
         <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.77</v>
+        <v>2.09</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>3.68</v>
       </c>
       <c r="O35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>4.42</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>4.13</v>
       </c>
       <c r="O37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N38" t="n">
         <v>2.6</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O38" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="M40" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="N40" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="M41" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="N41" t="n">
-        <v>4.51</v>
+        <v>4.41</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,41 +5772,41 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>4.36</v>
+        <v>3.86</v>
       </c>
       <c r="N45" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="O45" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="P45" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="R45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U45" t="n">
         <v>1.37</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V45" t="n">
-        <v>6.05</v>
+        <v>6.65</v>
       </c>
       <c r="W45" t="n">
         <v>1.08</v>
@@ -5815,34 +5815,34 @@
         <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
         <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,37 +5895,37 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="M46" t="n">
-        <v>3.86</v>
+        <v>4.36</v>
       </c>
       <c r="N46" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="O46" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P46" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S46" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U46" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V46" t="n">
-        <v>6.65</v>
+        <v>6.05</v>
       </c>
       <c r="W46" t="n">
         <v>1.08</v>
@@ -5934,34 +5934,34 @@
         <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG46" t="n">
         <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -778,70 +778,70 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="O3" t="n">
-        <v>4.89</v>
+        <v>4.78</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>8.4</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
         <v>1.19</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.65</v>
+        <v>1.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.45</v>
+        <v>4.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>7.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>4.62</v>
+        <v>1.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="N11" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
       <c r="M13" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="N13" t="n">
-        <v>1.82</v>
+        <v>4.38</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>4.63</v>
+        <v>3.84</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.7</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>5.25</v>
+        <v>4.63</v>
       </c>
       <c r="N16" t="n">
-        <v>6.06</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.88</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>4.93</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>7.66</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="W21" t="n">
         <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.31</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="P23" t="n">
         <v>2.03</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="T23" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>4.93</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>1.36</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>7.66</v>
+        <v>2.07</v>
       </c>
       <c r="P24" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.83</v>
+        <v>4.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.01</v>
+        <v>2.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>4.16</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
         <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="O27" t="n">
-        <v>3.97</v>
+        <v>4.16</v>
       </c>
       <c r="P27" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.06</v>
+        <v>1.66</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N28" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.1</v>
+        <v>2.94</v>
       </c>
       <c r="O29" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O30" t="n">
         <v>2.8</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V31" t="n">
-        <v>5.55</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
         <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.33</v>
+        <v>1.39</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.66</v>
+        <v>3.06</v>
       </c>
       <c r="M32" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.35</v>
+        <v>3.65</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>1.92</v>
       </c>
       <c r="O33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N34" t="n">
-        <v>5.37</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="N35" t="n">
-        <v>3.68</v>
+        <v>4.13</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="M37" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>4.13</v>
+        <v>3.68</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>5.37</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.69</v>
+        <v>1.18</v>
       </c>
       <c r="M40" t="n">
-        <v>3.96</v>
+        <v>10.8</v>
       </c>
       <c r="N40" t="n">
-        <v>4.51</v>
+        <v>13.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>4.41</v>
+        <v>4.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="M42" t="n">
-        <v>10.8</v>
+        <v>7.5</v>
       </c>
       <c r="N42" t="n">
-        <v>13.1</v>
+        <v>10.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>7.5</v>
+        <v>3.99</v>
       </c>
       <c r="N43" t="n">
-        <v>10.6</v>
+        <v>4.41</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="M7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.65</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="N8" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.45</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>1.46</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="N12" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3.82</v>
+        <v>5.25</v>
       </c>
       <c r="N13" t="n">
-        <v>4.38</v>
+        <v>6.06</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>3.88</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.09</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.82</v>
+        <v>5.3</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.95</v>
+        <v>3.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="N14" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
-        <v>5.25</v>
+        <v>3.82</v>
       </c>
       <c r="N15" t="n">
-        <v>6.06</v>
+        <v>4.38</v>
       </c>
       <c r="O15" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V15" t="n">
         <v>5.75</v>
       </c>
-      <c r="R15" t="n">
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.19</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z15" t="n">
-        <v>5.3</v>
+        <v>3.82</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.24</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>4.93</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.36</v>
-      </c>
-      <c r="O21" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.01</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6</v>
+        <v>3.62</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>4.13</v>
       </c>
       <c r="O22" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>3.78</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
         <v>3.2</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AH23" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>5.55</v>
+        <v>7.1</v>
       </c>
       <c r="W24" t="n">
         <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.33</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.29</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AB25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T26" t="n">
         <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.89</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,74 +3630,74 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O27" t="n">
-        <v>4.16</v>
+        <v>3.78</v>
       </c>
       <c r="P27" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD27" t="n">
         <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
         <v>1.3</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.66</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>4.93</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>7.66</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.31</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>2.94</v>
+        <v>5.37</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>3.06</v>
       </c>
       <c r="M30" t="n">
         <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>2.24</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>2.3</v>
+        <v>4.42</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.06</v>
+        <v>2.13</v>
       </c>
       <c r="M32" t="n">
         <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.24</v>
+        <v>3.29</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.65</v>
+        <v>1.66</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.92</v>
+        <v>4.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>3.68</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.82</v>
+        <v>3.15</v>
       </c>
       <c r="M35" t="n">
-        <v>3.62</v>
+        <v>2.6</v>
       </c>
       <c r="N35" t="n">
-        <v>4.13</v>
+        <v>2.7</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>4.42</v>
+        <v>2.08</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.68</v>
+        <v>2.94</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>3.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>5.37</v>
+        <v>1.92</v>
       </c>
       <c r="O38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
         <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.18</v>
+        <v>1.69</v>
       </c>
       <c r="M40" t="n">
-        <v>10.8</v>
+        <v>3.96</v>
       </c>
       <c r="N40" t="n">
-        <v>13.1</v>
+        <v>4.51</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="M41" t="n">
-        <v>3.96</v>
+        <v>7.5</v>
       </c>
       <c r="N41" t="n">
-        <v>4.51</v>
+        <v>10.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,16 +5345,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="M42" t="n">
-        <v>7.5</v>
+        <v>10.8</v>
       </c>
       <c r="N42" t="n">
-        <v>10.6</v>
+        <v>13.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5470,10 +5470,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,77 +5653,77 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="N44" t="n">
-        <v>6.15</v>
+        <v>7.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="P44" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S44" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="T44" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U44" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V44" t="n">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="W44" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="M46" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="O46" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="P46" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.5</v>
+        <v>5.95</v>
       </c>
       <c r="R46" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="T46" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>6.05</v>
+        <v>6.35</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="M4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3.1</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46077.375</v>
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46077.4375</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.5</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>4.39</v>
       </c>
       <c r="O7" t="n">
-        <v>7.8</v>
+        <v>2.55</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.09</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4.39</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>7.8</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.25</v>
       </c>
-      <c r="V8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.61458333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>7.31</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="N12" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>2.47</v>
       </c>
       <c r="M13" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>6.06</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5</v>
+        <v>5.52</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.59</v>
+        <v>2.07</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.05</v>
+        <v>2.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.24</v>
+        <v>1.91</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.96</v>
+        <v>4.63</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N15" t="n">
         <v>1.73</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.38</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.3</v>
+        <v>4.43</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="T15" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="U15" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="N22" t="n">
-        <v>4.13</v>
+        <v>4.42</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.3</v>
+        <v>3.68</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
         <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
         <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.56</v>
+        <v>2.31</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>2.94</v>
       </c>
       <c r="O25" t="n">
-        <v>2.07</v>
+        <v>3.04</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>5.55</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
         <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>1.56</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>2.07</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="R26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.37</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>1.82</v>
       </c>
       <c r="M28" t="n">
-        <v>4.93</v>
+        <v>3.62</v>
       </c>
       <c r="N28" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.36</v>
       </c>
-      <c r="O28" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="V28" t="n">
+        <v>7</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.3</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE28" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="N29" t="n">
-        <v>5.37</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>2.19</v>
+        <v>3.97</v>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>2.98</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.84</v>
+        <v>2.47</v>
       </c>
       <c r="T29" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
         <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.71</v>
+        <v>4.15</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.21</v>
+        <v>1.32</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.06</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>4.93</v>
       </c>
       <c r="N30" t="n">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>7.66</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AB30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.8</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="N31" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.29</v>
+        <v>2.08</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4357,40 +4357,40 @@
         <v>4.6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA33" t="n">
         <v>1.6</v>
@@ -4399,22 +4399,22 @@
         <v>2.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC34" t="n">
         <v>3.5</v>
       </c>
-      <c r="N34" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
+      <c r="AD34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4582,77 +4582,77 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="M35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
         <v>2.6</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.24</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V35" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O36" t="n">
-        <v>4.16</v>
+        <v>2.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="T36" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V36" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF36" t="n">
         <v>1.95</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.31</v>
+        <v>1.65</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>2.94</v>
+        <v>5.37</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N38" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.69</v>
+        <v>1.27</v>
       </c>
       <c r="M40" t="n">
-        <v>3.96</v>
+        <v>7.5</v>
       </c>
       <c r="N40" t="n">
-        <v>4.51</v>
+        <v>10.6</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>3.26</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>7.5</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>10.6</v>
+        <v>4.51</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.18</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>10.8</v>
+        <v>3.99</v>
       </c>
       <c r="N42" t="n">
-        <v>13.1</v>
+        <v>4.41</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>1.18</v>
       </c>
       <c r="M43" t="n">
-        <v>3.99</v>
+        <v>10.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4.41</v>
+        <v>13.1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF43" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M45" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>5.9</v>
+        <v>6.15</v>
       </c>
       <c r="O45" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="R45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U45" t="n">
         <v>1.4</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V45" t="n">
-        <v>6.65</v>
+        <v>6.35</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AF45" t="n">
         <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N46" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O46" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S46" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V46" t="n">
-        <v>6.35</v>
+        <v>6.65</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="n">
         <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="N9" t="n">
         <v>7</v>
@@ -1513,7 +1513,7 @@
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
         <v>2.12</v>
@@ -1522,7 +1522,7 @@
         <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
         <v>1.2</v>
@@ -1555,10 +1555,10 @@
         <v>2.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.61458333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>7.31</v>
+        <v>1.46</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.47</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.63</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>3.93</v>
       </c>
       <c r="M14" t="n">
-        <v>4.63</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.93</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>7.31</v>
       </c>
       <c r="O15" t="n">
-        <v>4.43</v>
+        <v>1.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="T15" t="n">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>2.9</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.8</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q16" t="n">
         <v>4</v>
       </c>
-      <c r="N16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="M21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC21" t="n">
         <v>3.1</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AD21" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z21" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.26</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.52</v>
+        <v>4.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.42</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>7.75</v>
+        <v>5.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.29</v>
+        <v>2.18</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.5</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
         <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="N25" t="n">
-        <v>2.94</v>
+        <v>4.42</v>
       </c>
       <c r="O25" t="n">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
-        <v>5.55</v>
+        <v>7.1</v>
       </c>
       <c r="W26" t="n">
         <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.33</v>
+        <v>1.39</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="N27" t="n">
-        <v>2.1</v>
+        <v>4.13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.78</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.77</v>
+        <v>4.85</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="M28" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4.13</v>
+        <v>2.94</v>
       </c>
       <c r="O28" t="n">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.85</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>2.6</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>5.37</v>
       </c>
       <c r="O29" t="n">
-        <v>3.97</v>
+        <v>2.19</v>
       </c>
       <c r="P29" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.47</v>
+        <v>2.84</v>
       </c>
       <c r="T29" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="U29" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
         <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.15</v>
+        <v>3.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.32</v>
+        <v>2.21</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8</v>
+        <v>3.18</v>
       </c>
       <c r="M30" t="n">
-        <v>4.93</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="O30" t="n">
-        <v>7.66</v>
+        <v>4.16</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.83</v>
       </c>
-      <c r="R30" t="n">
+      <c r="AF30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.01</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,77 +4225,77 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="O32" t="n">
-        <v>4.16</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
         <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AF32" t="n">
         <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.66</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
-        <v>4.05</v>
+        <v>4.93</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="O33" t="n">
-        <v>1.98</v>
+        <v>7.66</v>
       </c>
       <c r="P33" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.18</v>
+        <v>1.83</v>
       </c>
       <c r="R33" t="n">
         <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="T33" t="n">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="V33" t="n">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
         <v>1.2</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O34" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
         <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S34" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.75</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.65</v>
+        <v>3.16</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>1.92</v>
+        <v>2.36</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T35" t="n">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="U35" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U36" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V36" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.65</v>
+        <v>3.11</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>5.37</v>
+        <v>2.18</v>
       </c>
       <c r="O37" t="n">
-        <v>2.19</v>
+        <v>3.84</v>
       </c>
       <c r="P37" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="U37" t="n">
         <v>1.36</v>
       </c>
       <c r="V37" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA37" t="n">
         <v>2.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.71</v>
+        <v>3.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.21</v>
+        <v>1.33</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T38" t="n">
         <v>2.8</v>
       </c>
-      <c r="M38" t="n">
+      <c r="U38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z38" t="n">
         <v>3.05</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V38" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="M39" t="n">
         <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>3.15</v>
+        <v>3.29</v>
       </c>
       <c r="O39" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="n">
         <v>1.32</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="M40" t="n">
-        <v>7.5</v>
+        <v>3.96</v>
       </c>
       <c r="N40" t="n">
-        <v>10.6</v>
+        <v>4.51</v>
       </c>
       <c r="O40" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="P40" t="n">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="R40" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>4.65</v>
+        <v>3.15</v>
       </c>
       <c r="T40" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="U40" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="V40" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="X40" t="n">
         <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.26</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AH40" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="M41" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
-        <v>4.51</v>
+        <v>4</v>
       </c>
       <c r="O41" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
         <v>1.29</v>
       </c>
       <c r="S41" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T41" t="n">
         <v>2.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
         <v>1.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA41" t="n">
         <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF41" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>1.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3.99</v>
+        <v>10.5</v>
       </c>
       <c r="N42" t="n">
-        <v>4.41</v>
+        <v>12.5</v>
       </c>
       <c r="O42" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W42" t="n">
         <v>1.29</v>
       </c>
-      <c r="S42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V42" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.11</v>
-      </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>3.55</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.95</v>
+        <v>7.17</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,37 +5538,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="M43" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>13.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P43" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="R43" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S43" t="n">
         <v>4.75</v>
       </c>
       <c r="T43" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U43" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V43" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="W43" t="n">
         <v>1.29</v>
@@ -5577,34 +5577,34 @@
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB43" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AH43" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI46"/>
+  <dimension ref="A1:AI47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46077.60416666666</v>
+        <v>46077.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>4.39</v>
       </c>
       <c r="O8" t="n">
-        <v>7.8</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.09</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.75</v>
+        <v>7.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.25</v>
+        <v>2.09</v>
       </c>
       <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>8</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.25</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46077.61458333334</v>
+        <v>46077.60416666666</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46077.65625</v>
+        <v>46077.61458333334</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46077.66666666666</v>
+        <v>46077.65625</v>
       </c>
     </row>
     <row r="12">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>2.47</v>
       </c>
       <c r="M12" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.63</v>
+        <v>3.96</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.93</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>7.31</v>
       </c>
       <c r="O14" t="n">
-        <v>4.43</v>
+        <v>1.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>2.9</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>3.48</v>
       </c>
       <c r="M15" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>7.31</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>1.75</v>
+        <v>4.43</v>
       </c>
       <c r="P15" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>4.05</v>
+        <v>3.28</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>2.49</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="V15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.9</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.47</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.63</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46077.6875</v>
+        <v>46077.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2944,52 +2944,52 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46077.69791666666</v>
+        <v>46077.6875</v>
       </c>
     </row>
     <row r="22">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>4.42</v>
       </c>
       <c r="O22" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.43</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.3</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH22" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>8.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.18</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>3.72</v>
+        <v>7.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="T23" t="n">
-        <v>3.01</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="M25" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>4.42</v>
+        <v>3.29</v>
       </c>
       <c r="O25" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.8</v>
+        <v>1.88</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.36</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V26" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>2.88</v>
       </c>
       <c r="M27" t="n">
-        <v>3.62</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.13</v>
+        <v>2.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.85</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="U27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.36</v>
       </c>
-      <c r="V27" t="n">
-        <v>7</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.31</v>
+        <v>3.06</v>
       </c>
       <c r="M28" t="n">
         <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.94</v>
+        <v>2.24</v>
       </c>
       <c r="O28" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
         <v>6.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>5.37</v>
+        <v>2.26</v>
       </c>
       <c r="O29" t="n">
-        <v>2.19</v>
+        <v>3.35</v>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R29" t="n">
         <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE29" t="n">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="O30" t="n">
-        <v>4.16</v>
+        <v>3.97</v>
       </c>
       <c r="P30" t="n">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V30" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.59</v>
+        <v>4.15</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.06</v>
+        <v>2.36</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="O31" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V31" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z31" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC31" t="n">
         <v>3.3</v>
       </c>
-      <c r="AA31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.12</v>
-      </c>
       <c r="AD31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,64 +4229,64 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V32" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AF32" t="n">
         <v>1.95</v>
@@ -4295,7 +4295,7 @@
         <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.77</v>
+        <v>2.19</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>8</v>
+        <v>1.57</v>
       </c>
       <c r="M33" t="n">
-        <v>4.93</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>1.36</v>
+        <v>5.5</v>
       </c>
       <c r="O33" t="n">
-        <v>7.66</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
         <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>2.58</v>
+        <v>2.47</v>
       </c>
       <c r="U33" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V33" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA33" t="n">
         <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N34" t="n">
-        <v>3.15</v>
+        <v>4.13</v>
       </c>
       <c r="O34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.8</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
         <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD34" t="n">
         <v>1.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.16</v>
+        <v>1.66</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
-        <v>3.97</v>
+        <v>1.98</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.98</v>
+        <v>5.18</v>
       </c>
       <c r="R35" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>3.24</v>
+        <v>2.25</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="V35" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="W35" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
         <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.15</v>
+        <v>2.39</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.32</v>
+        <v>2.38</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4701,77 +4701,77 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>3.11</v>
       </c>
       <c r="M36" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>3.84</v>
       </c>
       <c r="P36" t="n">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T36" t="n">
-        <v>2.47</v>
+        <v>3.02</v>
       </c>
       <c r="U36" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V36" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="W36" t="n">
         <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.11</v>
+        <v>2.31</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.18</v>
+        <v>2.94</v>
       </c>
       <c r="O37" t="n">
-        <v>3.84</v>
+        <v>3.04</v>
       </c>
       <c r="P37" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="T37" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W37" t="n">
         <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AF37" t="n">
         <v>2</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4943,19 +4943,19 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="M38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O38" t="n">
         <v>3.1</v>
       </c>
-      <c r="N38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3.15</v>
-      </c>
       <c r="P38" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
         <v>3.2</v>
@@ -4964,40 +4964,40 @@
         <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T38" t="n">
         <v>2.8</v>
       </c>
       <c r="U38" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA38" t="n">
         <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC38" t="n">
         <v>3.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE38" t="n">
         <v>1.75</v>
@@ -5006,10 +5006,10 @@
         <v>1.93</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.13</v>
+        <v>3.18</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>3.29</v>
+        <v>2.2</v>
       </c>
       <c r="O39" t="n">
-        <v>2.88</v>
+        <v>4.16</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="R39" t="n">
         <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="T39" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U39" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V39" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
         <v>1.29</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
         <v>1.78</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5140,12 +5140,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,76 +5181,76 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.69</v>
+        <v>3.65</v>
       </c>
       <c r="M40" t="n">
-        <v>3.96</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>4.51</v>
+        <v>1.92</v>
       </c>
       <c r="O40" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.75</v>
+        <v>2.45</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U40" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V40" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W40" t="n">
         <v>1.09</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF40" t="n">
         <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.15</v>
+        <v>1.22</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>46077.70833333334</v>
+        <v>46077.69791666666</v>
       </c>
     </row>
     <row r="41">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,22 +5419,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="M42" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="N42" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P42" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="R42" t="n">
         <v>1.15</v>
@@ -5443,13 +5443,13 @@
         <v>4.75</v>
       </c>
       <c r="T42" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U42" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V42" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="W42" t="n">
         <v>1.29</v>
@@ -5458,34 +5458,34 @@
         <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AH42" t="n">
-        <v>7.17</v>
+        <v>4.1</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,22 +5538,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="N43" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="O43" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="P43" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="R43" t="n">
         <v>1.15</v>
@@ -5562,13 +5562,13 @@
         <v>4.75</v>
       </c>
       <c r="T43" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U43" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V43" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="W43" t="n">
         <v>1.29</v>
@@ -5577,34 +5577,34 @@
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB43" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AH43" t="n">
-        <v>4.1</v>
+        <v>7.17</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5616,27 +5616,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5653,80 +5653,80 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="M44" t="n">
-        <v>4.36</v>
+        <v>3.96</v>
       </c>
       <c r="N44" t="n">
-        <v>7.8</v>
+        <v>4.51</v>
       </c>
       <c r="O44" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="P44" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="R44" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="S44" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="T44" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1.42</v>
       </c>
-      <c r="V44" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE44" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.84</v>
+        <v>2.15</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46077.875</v>
+        <v>46077.70833333334</v>
       </c>
     </row>
     <row r="45">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="N45" t="n">
-        <v>6.15</v>
+        <v>5.9</v>
       </c>
       <c r="O45" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="P45" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="R45" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V45" t="n">
-        <v>6.35</v>
+        <v>6.65</v>
       </c>
       <c r="W45" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
         <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,41 +5891,41 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="M46" t="n">
-        <v>3.86</v>
+        <v>4.36</v>
       </c>
       <c r="N46" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="O46" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P46" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S46" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U46" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V46" t="n">
-        <v>6.65</v>
+        <v>6.05</v>
       </c>
       <c r="W46" t="n">
         <v>1.08</v>
@@ -5934,36 +5934,155 @@
         <v>1.03</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG46" t="n">
         <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="AI46" s="3" t="n">
+        <v>46077.875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V47" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AI47" s="3" t="n">
         <v>46077.875</v>
       </c>
     </row>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="M8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>4.39</v>
+        <v>4.49</v>
       </c>
       <c r="O8" t="n">
         <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
         <v>3.25</v>
@@ -1403,16 +1403,16 @@
         <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Z8" t="n">
         <v>2.25</v>
@@ -1421,7 +1421,7 @@
         <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
         <v>5.5</v>
@@ -1436,10 +1436,10 @@
         <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.5</v>
+        <v>6.66</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>7.8</v>
+        <v>6.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="R9" t="n">
         <v>1.44</v>
@@ -1546,16 +1546,16 @@
         <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
         <v>1.1</v>
@@ -1617,13 +1617,13 @@
         <v>5.6</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="P10" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="Q10" t="n">
         <v>6.25</v>
@@ -1638,13 +1638,13 @@
         <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.47</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>1.46</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.96</v>
+        <v>4.63</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>3.48</v>
       </c>
       <c r="M14" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>7.31</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>1.75</v>
+        <v>4.43</v>
       </c>
       <c r="P14" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>4.05</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.48</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q16" t="n">
         <v>6</v>
       </c>
-      <c r="M16" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.8</v>
+        <v>1.75</v>
       </c>
       <c r="M17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="N17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>3.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.42</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>4.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>2.76</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>8.75</v>
+        <v>3.16</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.35</v>
+        <v>2.36</v>
       </c>
       <c r="O23" t="n">
-        <v>7.5</v>
+        <v>3.97</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8</v>
+        <v>2.98</v>
       </c>
       <c r="R23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.31</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC24" t="n">
         <v>3.5</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,61 +3396,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.29</v>
+        <v>2.26</v>
       </c>
       <c r="O25" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.4</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
         <v>1.73</v>
@@ -3459,10 +3459,10 @@
         <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,77 +3511,77 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="O26" t="n">
         <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.38</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V26" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
         <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG26" t="n">
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.06</v>
+        <v>2.31</v>
       </c>
       <c r="M28" t="n">
         <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
         <v>6.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,53 +3868,53 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2.26</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z29" t="n">
         <v>3.35</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.12</v>
       </c>
       <c r="AA29" t="n">
         <v>1.95</v>
@@ -3923,22 +3923,22 @@
         <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.16</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>2.36</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>3.97</v>
+        <v>2.19</v>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.98</v>
+        <v>5.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.47</v>
+        <v>2.87</v>
       </c>
       <c r="T30" t="n">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="U30" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
         <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.32</v>
+        <v>2.19</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
         <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U31" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4225,32 +4225,32 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.65</v>
+        <v>3.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="O32" t="n">
-        <v>2.19</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.7</v>
+        <v>2.45</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>2.6</v>
@@ -4265,37 +4265,37 @@
         <v>1.09</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.19</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="N33" t="n">
-        <v>5.5</v>
+        <v>4.13</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="R33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.3</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V33" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE33" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="M34" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>4.13</v>
+        <v>2.58</v>
       </c>
       <c r="O34" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="P34" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="T34" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
         <v>7</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="AA34" t="n">
         <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.66</v>
+        <v>2.13</v>
       </c>
       <c r="M35" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>3.29</v>
       </c>
       <c r="O35" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="P35" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.18</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z35" t="n">
         <v>3.3</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V35" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AA35" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.39</v>
+        <v>3.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="O36" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
         <v>2.8</v>
       </c>
       <c r="T36" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="U36" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V36" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG36" t="n">
         <v>1.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.31</v>
+        <v>8.75</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.94</v>
+        <v>1.35</v>
       </c>
       <c r="O37" t="n">
-        <v>3.04</v>
+        <v>7.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S37" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="T37" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
         <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AF37" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,22 +4943,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="P38" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R38" t="n">
         <v>1.38</v>
@@ -4967,49 +4967,49 @@
         <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="U38" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V38" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
         <v>1.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF38" t="n">
         <v>2</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG38" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,25 +5062,25 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
-        <v>4.16</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S39" t="n">
         <v>2.8</v>
@@ -5092,43 +5092,43 @@
         <v>1.38</v>
       </c>
       <c r="V39" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE39" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.65</v>
+        <v>1.66</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N40" t="n">
-        <v>1.92</v>
+        <v>4.6</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>1.98</v>
       </c>
       <c r="P40" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.45</v>
+        <v>5.18</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="V40" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W40" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="N41" t="n">
-        <v>4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="R41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.29</v>
       </c>
-      <c r="S41" t="n">
+      <c r="X41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB41" t="n">
         <v>3.3</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W41" t="n">
+      <c r="AC41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.11</v>
       </c>
-      <c r="X41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH41" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V42" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.25</v>
       </c>
-      <c r="M42" t="n">
-        <v>8</v>
-      </c>
-      <c r="N42" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH42" t="n">
-        <v>4.1</v>
+        <v>1.95</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5541,10 +5541,10 @@
         <v>1.15</v>
       </c>
       <c r="M43" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="N43" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="O43" t="n">
         <v>1.4</v>
@@ -5553,7 +5553,7 @@
         <v>3.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="R43" t="n">
         <v>1.15</v>
@@ -5568,7 +5568,7 @@
         <v>1.95</v>
       </c>
       <c r="V43" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="W43" t="n">
         <v>1.29</v>
@@ -5601,10 +5601,10 @@
         <v>1.85</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AH43" t="n">
-        <v>7.17</v>
+        <v>6</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T4" t="n">
         <v>2.7</v>
@@ -930,7 +930,7 @@
         <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
@@ -948,7 +948,7 @@
         <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="AD4" t="n">
         <v>1.3</v>
@@ -957,13 +957,13 @@
         <v>1.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
         <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46077.375</v>
@@ -1144,22 +1144,22 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
         <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
         <v>1.38</v>
@@ -1180,13 +1180,13 @@
         <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AB6" t="n">
         <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD6" t="n">
         <v>1.3</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>6.66</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.49</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>6.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>2.07</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.66</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>1.48</v>
+        <v>4.49</v>
       </c>
       <c r="O9" t="n">
-        <v>6.1</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.07</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1632,16 +1632,16 @@
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
         <v>2.12</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="W10" t="n">
         <v>1.18</v>
@@ -1650,13 +1650,13 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
         <v>5.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
         <v>2.75</v>
@@ -1674,7 +1674,7 @@
         <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
         <v>2.8</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="N12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.63</v>
+        <v>3.96</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.48</v>
+        <v>4.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="O14" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>3.96</v>
+        <v>4.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>7.31</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.36</v>
       </c>
-      <c r="M16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
         <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.75</v>
+        <v>3.48</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3.75</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
-        <v>2.3</v>
+        <v>4.43</v>
       </c>
       <c r="P17" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>5.52</v>
+        <v>4.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.91</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46077.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46077.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46077.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="M22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O22" t="n">
         <v>3.3</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.16</v>
-      </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.59</v>
+        <v>3.68</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.16</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.36</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
-        <v>3.97</v>
+        <v>2.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.98</v>
+        <v>4.85</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.95</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>4.42</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P24" t="n">
         <v>2.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
         <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V24" t="n">
-        <v>7.75</v>
+        <v>5.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="O25" t="n">
-        <v>3.35</v>
+        <v>3.97</v>
       </c>
       <c r="P25" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="V25" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z25" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.96</v>
+        <v>2.36</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.68</v>
+        <v>2.87</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
         <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.18</v>
+        <v>3.62</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AC26" t="n">
         <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.88</v>
+        <v>1.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="P27" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="T27" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.23</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.96</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.31</v>
+        <v>8.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.94</v>
+        <v>1.35</v>
       </c>
       <c r="O28" t="n">
-        <v>3.04</v>
+        <v>7.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="T28" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>5.11</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>6.9</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
-        <v>2.19</v>
+        <v>2.85</v>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U30" t="n">
         <v>1.42</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="W30" t="n">
         <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.65</v>
+        <v>3.12</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.19</v>
+        <v>1.55</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.57</v>
+        <v>3.11</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>3.84</v>
       </c>
       <c r="P31" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2.47</v>
+        <v>3.02</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.74</v>
+        <v>2.95</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.12</v>
+        <v>1.19</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,58 +4229,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AD32" t="n">
         <v>1.3</v>
@@ -4289,13 +4289,13 @@
         <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,70 +4348,70 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="M33" t="n">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="N33" t="n">
-        <v>4.13</v>
+        <v>4.42</v>
       </c>
       <c r="O33" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC33" t="n">
         <v>3.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF33" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
         <v>1.95</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.36</v>
+        <v>1.88</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="O34" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="T34" t="n">
         <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.13</v>
+        <v>3.18</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.29</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
-        <v>2.88</v>
+        <v>4.16</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V35" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
         <v>1.29</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB35" t="n">
         <v>1.78</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.06</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>2.24</v>
+        <v>3.67</v>
       </c>
       <c r="O36" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="P36" t="n">
         <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T36" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="U36" t="n">
         <v>1.38</v>
       </c>
       <c r="V36" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="AE36" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC36" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>8.75</v>
+        <v>3.65</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="O37" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="R37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V37" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,22 +4943,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.11</v>
+        <v>2.61</v>
       </c>
       <c r="M38" t="n">
         <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="O38" t="n">
-        <v>3.84</v>
+        <v>3.24</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
         <v>1.38</v>
@@ -4967,49 +4967,49 @@
         <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="U38" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V38" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
         <v>1.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB38" t="n">
         <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
         <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P39" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="R39" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T39" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U39" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z39" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AA39" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="M40" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="P40" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.18</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V40" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.3</v>
       </c>
-      <c r="S40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V40" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE40" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="M41" t="n">
-        <v>6.4</v>
+        <v>3.96</v>
       </c>
       <c r="N41" t="n">
-        <v>8.300000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="O41" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="P41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S41" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S41" t="n">
-        <v>4.75</v>
-      </c>
       <c r="T41" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="U41" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M42" t="n">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="N42" t="n">
-        <v>4.26</v>
+        <v>4.74</v>
       </c>
       <c r="O42" t="n">
         <v>2.3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>5.04</v>
       </c>
       <c r="R42" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S42" t="n">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="T42" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U42" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V42" t="n">
-        <v>5.45</v>
+        <v>6.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
         <v>1.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
         <v>2.62</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
         <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5565,10 +5565,10 @@
         <v>1.75</v>
       </c>
       <c r="U43" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="V43" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="W43" t="n">
         <v>1.29</v>
@@ -5595,10 +5595,10 @@
         <v>2.1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
         <v>1.06</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="M44" t="n">
-        <v>3.96</v>
+        <v>6.3</v>
       </c>
       <c r="N44" t="n">
-        <v>4.51</v>
+        <v>10</v>
       </c>
       <c r="O44" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="P44" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S44" t="n">
         <v>4.75</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.29</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.09</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.62</v>
+        <v>1.79</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,77 +5891,77 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="M46" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>7.8</v>
+        <v>6.15</v>
       </c>
       <c r="O46" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="P46" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.5</v>
+        <v>5.95</v>
       </c>
       <c r="R46" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="T46" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U46" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>6.05</v>
+        <v>6.35</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="N47" t="n">
-        <v>6.15</v>
+        <v>7.8</v>
       </c>
       <c r="O47" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="P47" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="T47" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U47" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V47" t="n">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="W47" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.66</v>
+        <v>1.88</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>4.49</v>
       </c>
       <c r="O8" t="n">
-        <v>6.1</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.07</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.88</v>
+        <v>6.66</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.49</v>
+        <v>1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>6.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>2.07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.63</v>
+        <v>3.96</v>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>3.48</v>
       </c>
       <c r="M13" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.8</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q14" t="n">
         <v>4</v>
       </c>
-      <c r="N14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>7.31</v>
+        <v>1.46</v>
       </c>
       <c r="O15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.75</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.3</v>
-      </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>5.52</v>
+        <v>4.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>5.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.86</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
         <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.48</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>4.63</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.23</v>
+        <v>7.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2.59</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>1.41</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.8</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AD18" t="n">
         <v>1.22</v>
       </c>
-      <c r="V18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE18" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46077.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7.6</v>
+        <v>3.97</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>2.83</v>
       </c>
       <c r="N19" t="n">
-        <v>1.41</v>
+        <v>2.07</v>
       </c>
       <c r="O19" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V19" t="n">
+        <v>10</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE19" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46077.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,61 +2801,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.51</v>
+        <v>3.23</v>
       </c>
       <c r="M20" t="n">
-        <v>3.48</v>
+        <v>2.59</v>
       </c>
       <c r="N20" t="n">
-        <v>6.67</v>
+        <v>2.47</v>
       </c>
       <c r="O20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V20" t="n">
+        <v>10</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2.2</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AE20" t="n">
         <v>2.25</v>
@@ -2864,10 +2864,10 @@
         <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46077.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.97</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>2.83</v>
+        <v>3.48</v>
       </c>
       <c r="N21" t="n">
-        <v>2.07</v>
+        <v>6.67</v>
       </c>
       <c r="O21" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="P21" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.57</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V21" t="n">
-        <v>10</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AG21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH21" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.88</v>
+        <v>8.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
-        <v>7.8</v>
+        <v>5.95</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.07</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.09</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.68</v>
+        <v>2.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,38 +3154,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="P23" t="n">
         <v>2.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="T23" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
         <v>6</v>
@@ -3194,37 +3194,37 @@
         <v>1.09</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>2.53</v>
       </c>
       <c r="T24" t="n">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.85</v>
+        <v>3.07</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.8</v>
+        <v>3.68</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.16</v>
+        <v>2.37</v>
       </c>
       <c r="M25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.1</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.36</v>
-      </c>
       <c r="O25" t="n">
-        <v>3.97</v>
+        <v>2.85</v>
       </c>
       <c r="P25" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.28</v>
       </c>
-      <c r="V25" t="n">
-        <v>8</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="O27" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8.75</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1.35</v>
+        <v>4.33</v>
       </c>
       <c r="O28" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.8</v>
+        <v>4.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N29" t="n">
-        <v>5.11</v>
+        <v>5.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="P29" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.37</v>
+        <v>1.81</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>4.42</v>
       </c>
       <c r="O30" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="T30" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="O31" t="n">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="P31" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>2.61</v>
       </c>
       <c r="M32" t="n">
         <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="O32" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
         <v>1.38</v>
@@ -4253,10 +4253,10 @@
         <v>2.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
         <v>6.5</v>
@@ -4265,37 +4265,37 @@
         <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.81</v>
+        <v>3.16</v>
       </c>
       <c r="M33" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="N33" t="n">
-        <v>4.42</v>
+        <v>2.36</v>
       </c>
       <c r="O33" t="n">
-        <v>2.4</v>
+        <v>3.97</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.75</v>
+        <v>2.98</v>
       </c>
       <c r="R33" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X33" t="n">
         <v>1.02</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z33" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.75</v>
+        <v>5.11</v>
       </c>
       <c r="O34" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="P34" t="n">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V34" t="n">
-        <v>6.9</v>
+        <v>5.25</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,40 +4586,40 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.18</v>
+        <v>2.26</v>
       </c>
       <c r="M35" t="n">
         <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="O35" t="n">
-        <v>4.16</v>
+        <v>2.88</v>
       </c>
       <c r="P35" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U35" t="n">
         <v>1.38</v>
       </c>
       <c r="V35" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
@@ -4628,31 +4628,31 @@
         <v>1.29</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>3.18</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.67</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
-        <v>2.6</v>
+        <v>4.16</v>
       </c>
       <c r="P36" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T36" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
         <v>1.38</v>
       </c>
       <c r="V36" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
         <v>3.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.78</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,58 +4824,58 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AD37" t="n">
         <v>1.3</v>
@@ -4884,13 +4884,13 @@
         <v>1.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.61</v>
+        <v>3.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>2.66</v>
+        <v>1.92</v>
       </c>
       <c r="O38" t="n">
-        <v>3.24</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V38" t="n">
+        <v>6</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC38" t="n">
         <v>3.1</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="O39" t="n">
-        <v>3.35</v>
+        <v>3.84</v>
       </c>
       <c r="P39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.03</v>
       </c>
-      <c r="Q39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V39" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O40" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S40" t="n">
         <v>2.7</v>
       </c>
       <c r="T40" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V40" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="W40" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.77</v>
+        <v>1.26</v>
       </c>
       <c r="M41" t="n">
-        <v>3.96</v>
+        <v>6.3</v>
       </c>
       <c r="N41" t="n">
-        <v>4.34</v>
+        <v>10</v>
       </c>
       <c r="O41" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="S41" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="T41" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="V41" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="W41" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.62</v>
+        <v>1.79</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3.86</v>
+        <v>9</v>
       </c>
       <c r="N42" t="n">
-        <v>4.74</v>
+        <v>13</v>
       </c>
       <c r="O42" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.04</v>
+        <v>9.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="S42" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="U42" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="V42" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="X42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y42" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y42" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AB42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD42" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC42" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE42" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AF42" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.15</v>
+        <v>1.77</v>
       </c>
       <c r="M43" t="n">
-        <v>9</v>
+        <v>3.96</v>
       </c>
       <c r="N43" t="n">
-        <v>13</v>
+        <v>4.34</v>
       </c>
       <c r="O43" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="U43" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="W43" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AB43" t="n">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.72</v>
+        <v>2.62</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="M44" t="n">
-        <v>6.3</v>
+        <v>3.86</v>
       </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>4.74</v>
       </c>
       <c r="O44" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.25</v>
+        <v>5.04</v>
       </c>
       <c r="R44" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="S44" t="n">
-        <v>4.75</v>
+        <v>2.88</v>
       </c>
       <c r="T44" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="U44" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="V44" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="W44" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5772,17 +5772,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
         <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="N45" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O45" t="n">
         <v>2.1</v>
@@ -5803,43 +5803,43 @@
         <v>2.7</v>
       </c>
       <c r="U45" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="W45" t="n">
         <v>1.08</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z45" t="n">
         <v>3.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC45" t="n">
         <v>3.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
         <v>2.25</v>
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
         <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V46" t="n">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="W46" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
         <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC46" t="n">
         <v>3.12</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG46" t="n">
         <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M47" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="O47" t="n">
         <v>1.91</v>
       </c>
       <c r="P47" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S47" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U47" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V47" t="n">
-        <v>6.05</v>
+        <v>6.75</v>
       </c>
       <c r="W47" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
         <v>1.27</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE47" t="n">
         <v>2.05</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -906,25 +906,25 @@
         <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>2.67</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
         <v>7.3</v>
@@ -933,22 +933,22 @@
         <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="AD4" t="n">
         <v>1.3</v>
@@ -957,7 +957,7 @@
         <v>1.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AG4" t="n">
         <v>1.35</v>
@@ -1144,46 +1144,46 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
         <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC6" t="n">
         <v>3.14</v>
@@ -1192,13 +1192,13 @@
         <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
         <v>1.7</v>
@@ -1617,7 +1617,7 @@
         <v>5.6</v>
       </c>
       <c r="N10" t="n">
-        <v>6.55</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.78</v>
@@ -1632,16 +1632,16 @@
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.18</v>
@@ -1650,16 +1650,16 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA10" t="n">
         <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AC10" t="n">
         <v>2.16</v>
@@ -1671,13 +1671,13 @@
         <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46077.61458333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>1.46</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.46</v>
+        <v>7.31</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.36</v>
       </c>
-      <c r="M16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
         <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.6</v>
+        <v>3.23</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>2.59</v>
       </c>
       <c r="N18" t="n">
-        <v>1.41</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>8</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46077.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,61 +2801,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.23</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
-        <v>2.59</v>
+        <v>3.48</v>
       </c>
       <c r="N20" t="n">
-        <v>2.47</v>
+        <v>6.67</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>2.84</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
         <v>2.25</v>
@@ -2864,10 +2864,10 @@
         <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46077.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>7.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>6.67</v>
+        <v>1.41</v>
       </c>
       <c r="O21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.2</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.38</v>
+        <v>1.09</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.75</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.35</v>
       </c>
-      <c r="O22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3170,7 +3170,7 @@
         <v>2.23</v>
       </c>
       <c r="P23" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
         <v>4.6</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="M24" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.05</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.3</v>
-      </c>
       <c r="O24" t="n">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>3.72</v>
       </c>
       <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.38</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.31</v>
       </c>
-      <c r="V24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="O25" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="AA25" t="n">
         <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.87</v>
+        <v>4.37</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.62</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.67</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>2.6</v>
+        <v>3.74</v>
       </c>
       <c r="P27" t="n">
         <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T27" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="U27" t="n">
         <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q28" t="n">
         <v>1.8</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.85</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>5.5</v>
+        <v>5.11</v>
       </c>
       <c r="O29" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>5.8</v>
+        <v>5.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AG29" t="n">
         <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>4.42</v>
+        <v>3.61</v>
       </c>
       <c r="O30" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AD30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="O31" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.42</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V31" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
         <v>1.09</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="M32" t="n">
         <v>3.3</v>
@@ -4241,37 +4241,37 @@
         <v>3.24</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AA32" t="n">
         <v>2.04</v>
@@ -4286,16 +4286,16 @@
         <v>1.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.16</v>
+        <v>1.88</v>
       </c>
       <c r="M33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC33" t="n">
         <v>3.1</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V33" t="n">
-        <v>8</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>4.15</v>
-      </c>
       <c r="AD33" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V34" t="n">
+        <v>8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.6</v>
       </c>
-      <c r="M34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V34" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AC34" t="n">
-        <v>2.39</v>
+        <v>4.15</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,28 +4586,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="M35" t="n">
         <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="O35" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S35" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="T35" t="n">
         <v>2.81</v>
@@ -4616,43 +4616,43 @@
         <v>1.38</v>
       </c>
       <c r="V35" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="M36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O36" t="n">
         <v>3.3</v>
       </c>
-      <c r="N36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4.16</v>
-      </c>
       <c r="P36" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U36" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V36" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.59</v>
+        <v>3.68</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,25 +4824,25 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="M37" t="n">
         <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>4.16</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
         <v>2.8</v>
@@ -4851,46 +4851,46 @@
         <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
         <v>1.29</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.12</v>
+        <v>3.59</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.65</v>
+        <v>1.57</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>1.92</v>
+        <v>5.5</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
+        <v>5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T38" t="n">
         <v>2.45</v>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.6</v>
-      </c>
       <c r="U38" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="V38" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AF38" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="P40" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="R40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U40" t="n">
         <v>1.38</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V40" t="n">
-        <v>6.9</v>
+        <v>6.55</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
         <v>1.27</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="AA40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.77</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="M41" t="n">
-        <v>6.3</v>
+        <v>3.86</v>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="O41" t="n">
-        <v>1.57</v>
+        <v>2.19</v>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="T41" t="n">
-        <v>1.92</v>
+        <v>2.47</v>
       </c>
       <c r="U41" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="V41" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="W41" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.3</v>
+        <v>2.13</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="M42" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="N42" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="P42" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>9.5</v>
+        <v>6.25</v>
       </c>
       <c r="R42" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S42" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="T42" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="U42" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="V42" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="W42" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X42" t="n">
         <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z42" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="AA42" t="n">
         <v>1.28</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AH42" t="n">
-        <v>6</v>
+        <v>3.88</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5538,40 +5538,40 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
         <v>3.96</v>
       </c>
       <c r="N43" t="n">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="O43" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="P43" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q43" t="n">
         <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="T43" t="n">
         <v>2.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V43" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="W43" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
@@ -5583,28 +5583,28 @@
         <v>4.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC43" t="n">
         <v>2.62</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="M44" t="n">
-        <v>3.86</v>
+        <v>9</v>
       </c>
       <c r="N44" t="n">
-        <v>4.74</v>
+        <v>13</v>
       </c>
       <c r="O44" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>3.94</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.04</v>
+        <v>12.13</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="S44" t="n">
-        <v>2.88</v>
+        <v>5.8</v>
       </c>
       <c r="T44" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="U44" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="V44" t="n">
-        <v>6.5</v>
+        <v>3.36</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="X44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y44" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y44" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AB44" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD44" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE44" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5779,52 +5779,52 @@
         <v>1.6</v>
       </c>
       <c r="M45" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="R45" t="n">
         <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T45" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V45" t="n">
         <v>6.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
         <v>1.28</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC45" t="n">
         <v>3.3</v>
@@ -5833,16 +5833,16 @@
         <v>1.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AF45" t="n">
         <v>1.73</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O46" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P46" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S46" t="n">
         <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U46" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V46" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="P47" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="R47" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U47" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V47" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
         <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AF47" t="n">
         <v>1.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>6.66</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.49</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>6.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>2.07</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.66</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>1.48</v>
+        <v>4.49</v>
       </c>
       <c r="O9" t="n">
-        <v>6.1</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.07</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.48</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>7.31</v>
+        <v>1.46</v>
       </c>
       <c r="O15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4.63</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="M17" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,34 +2563,34 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.23</v>
+        <v>3.97</v>
       </c>
       <c r="M18" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>2.07</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
         <v>10</v>
@@ -2599,37 +2599,37 @@
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46077.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.97</v>
+        <v>3.23</v>
       </c>
       <c r="M19" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="N19" t="n">
-        <v>2.07</v>
+        <v>2.47</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="S19" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V19" t="n">
         <v>10</v>
@@ -2718,37 +2718,37 @@
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46077.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>2.26</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="R22" t="n">
         <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
         <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.65</v>
+        <v>3.16</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>2.36</v>
       </c>
       <c r="O23" t="n">
-        <v>2.23</v>
+        <v>3.97</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.05</v>
+        <v>4.15</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.96</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="M24" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
         <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AA25" t="n">
         <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.32</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>4.37</v>
+        <v>5.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.41</v>
+        <v>2.12</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
         <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T26" t="n">
-        <v>3.02</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.54</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
         <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>3.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.74</v>
+        <v>2.6</v>
       </c>
       <c r="P27" t="n">
         <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>5.11</v>
+        <v>2.26</v>
       </c>
       <c r="O29" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.05</v>
+        <v>2.95</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.25</v>
+        <v>3.12</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,37 +3991,37 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>3.11</v>
       </c>
       <c r="M30" t="n">
         <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.61</v>
+        <v>2.18</v>
       </c>
       <c r="O30" t="n">
-        <v>2.6</v>
+        <v>3.84</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U30" t="n">
         <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W30" t="n">
         <v>1.08</v>
@@ -4030,34 +4030,34 @@
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AD30" t="n">
         <v>1.24</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.68</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>1.19</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>5.11</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="P33" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V33" t="n">
-        <v>6.9</v>
+        <v>5.25</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.77</v>
+        <v>2.33</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O34" t="n">
-        <v>3.97</v>
+        <v>3.74</v>
       </c>
       <c r="P34" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="T34" t="n">
-        <v>3.24</v>
+        <v>2.81</v>
       </c>
       <c r="U34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.28</v>
       </c>
-      <c r="V34" t="n">
-        <v>8</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE34" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AG34" t="n">
         <v>1.31</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,28 +4586,28 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="N35" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="P35" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="R35" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T35" t="n">
         <v>2.81</v>
@@ -4616,25 +4616,25 @@
         <v>1.38</v>
       </c>
       <c r="V35" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC35" t="n">
         <v>3.12</v>
@@ -4643,16 +4643,16 @@
         <v>1.28</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.18</v>
+        <v>1.85</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="O37" t="n">
-        <v>4.16</v>
+        <v>2.37</v>
       </c>
       <c r="P37" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.76</v>
+        <v>4.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U37" t="n">
         <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>7.5</v>
+        <v>6.55</v>
       </c>
       <c r="W37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X37" t="n">
         <v>1.03</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>5.5</v>
+        <v>4.37</v>
       </c>
       <c r="O38" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
         <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z38" t="n">
         <v>3.05</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AA38" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.11</v>
+        <v>2.36</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.18</v>
+        <v>2.87</v>
       </c>
       <c r="O39" t="n">
-        <v>3.84</v>
+        <v>2.9</v>
       </c>
       <c r="P39" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="R39" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="T39" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
         <v>3.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.85</v>
+        <v>3.18</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
-        <v>2.37</v>
+        <v>4.16</v>
       </c>
       <c r="P40" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.9</v>
+        <v>2.76</v>
       </c>
       <c r="R40" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U40" t="n">
         <v>1.38</v>
       </c>
       <c r="V40" t="n">
-        <v>6.55</v>
+        <v>7.5</v>
       </c>
       <c r="W40" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z40" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE40" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.95</v>
+        <v>1.26</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="M41" t="n">
-        <v>3.86</v>
+        <v>6.75</v>
       </c>
       <c r="N41" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>3.15</v>
+        <v>4.65</v>
       </c>
       <c r="T41" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="U41" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="V41" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="X41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="Z41" t="n">
-        <v>4</v>
+        <v>6.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.13</v>
+        <v>3.26</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.39</v>
+        <v>2.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AF41" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.15</v>
+        <v>3.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="M42" t="n">
-        <v>6.75</v>
+        <v>3.86</v>
       </c>
       <c r="N42" t="n">
-        <v>9.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="O42" t="n">
-        <v>1.57</v>
+        <v>2.19</v>
       </c>
       <c r="P42" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="R42" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S42" t="n">
-        <v>4.65</v>
+        <v>3.15</v>
       </c>
       <c r="T42" t="n">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="U42" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="V42" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.9</v>
+        <v>4</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.26</v>
+        <v>2.13</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.08</v>
+        <v>1.39</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.88</v>
+        <v>2.15</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M43" t="n">
+        <v>9</v>
+      </c>
+      <c r="N43" t="n">
+        <v>13</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T43" t="n">
         <v>1.75</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V43" t="n">
         <v>3.36</v>
       </c>
-      <c r="T43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V43" t="n">
-        <v>5.45</v>
-      </c>
       <c r="W43" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC43" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB43" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AD43" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>9</v>
+        <v>3.96</v>
       </c>
       <c r="N44" t="n">
-        <v>13</v>
+        <v>4.28</v>
       </c>
       <c r="O44" t="n">
-        <v>1.41</v>
+        <v>2.29</v>
       </c>
       <c r="P44" t="n">
-        <v>3.94</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>12.13</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V44" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.12</v>
-      </c>
-      <c r="S44" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V44" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.3</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AA44" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG44" t="n">
         <v>1.28</v>
       </c>
-      <c r="AB44" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD44" t="n">
+      <c r="AH44" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>5.7</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O45" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="P45" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="R45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U45" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.37</v>
       </c>
       <c r="V45" t="n">
         <v>6.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
         <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.33</v>
+        <v>2.84</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="P46" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="T46" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V46" t="n">
         <v>6.75</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE46" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.84</v>
+        <v>2.33</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.66</v>
+        <v>1.88</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>4.49</v>
       </c>
       <c r="O8" t="n">
-        <v>6.1</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.07</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.88</v>
+        <v>6.66</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.49</v>
+        <v>1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>6.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>2.07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>1.46</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.48</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>7.31</v>
       </c>
       <c r="O14" t="n">
-        <v>4.43</v>
+        <v>1.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>3.28</v>
+        <v>4.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.19</v>
+        <v>2.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>2.9</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="M16" t="n">
-        <v>4.63</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>4.75</v>
+        <v>4.63</v>
       </c>
       <c r="N17" t="n">
-        <v>7.31</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,34 +2563,34 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.97</v>
+        <v>3.23</v>
       </c>
       <c r="M18" t="n">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="N18" t="n">
-        <v>2.07</v>
+        <v>2.47</v>
       </c>
       <c r="O18" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="S18" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T18" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V18" t="n">
         <v>10</v>
@@ -2599,37 +2599,37 @@
         <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46077.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.23</v>
+        <v>3.97</v>
       </c>
       <c r="M19" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="N19" t="n">
-        <v>2.47</v>
+        <v>2.07</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
         <v>10</v>
@@ -2718,37 +2718,37 @@
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46077.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.51</v>
+        <v>7.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N20" t="n">
-        <v>6.67</v>
+        <v>1.41</v>
       </c>
       <c r="O20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.2</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.38</v>
+        <v>1.09</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46077.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>7.6</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="N21" t="n">
-        <v>1.41</v>
+        <v>6.67</v>
       </c>
       <c r="O21" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH21" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.09</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,65 +3035,65 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>3.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>2.23</v>
+        <v>4.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.6</v>
+        <v>2.76</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.05</v>
+        <v>3.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
         <v>1.74</v>
@@ -3102,10 +3102,10 @@
         <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.96</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.16</v>
+        <v>2.36</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.36</v>
+        <v>2.87</v>
       </c>
       <c r="O23" t="n">
-        <v>3.97</v>
+        <v>2.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>2.28</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.37</v>
+        <v>3.1</v>
       </c>
       <c r="M25" t="n">
         <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.93</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
-        <v>3.02</v>
+        <v>3.74</v>
       </c>
       <c r="P25" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.56</v>
+        <v>2.85</v>
       </c>
       <c r="R25" t="n">
         <v>1.39</v>
@@ -3441,10 +3441,10 @@
         <v>3.38</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
         <v>3.12</v>
@@ -3453,16 +3453,16 @@
         <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>5.5</v>
+        <v>4.37</v>
       </c>
       <c r="O26" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
         <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z26" t="n">
         <v>3.05</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,37 +3634,37 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>3.11</v>
       </c>
       <c r="M27" t="n">
         <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.61</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U27" t="n">
         <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.08</v>
@@ -3673,34 +3673,34 @@
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
         <v>1.24</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>1.19</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>8.75</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.35</v>
+        <v>5.5</v>
       </c>
       <c r="O28" t="n">
-        <v>7.5</v>
+        <v>2.12</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>2.26</v>
+        <v>3.05</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z29" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC29" t="n">
         <v>3.12</v>
       </c>
-      <c r="AA29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.11</v>
+        <v>1.58</v>
       </c>
       <c r="M30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S30" t="n">
         <v>3.3</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.65</v>
-      </c>
       <c r="T30" t="n">
-        <v>3.02</v>
+        <v>2.34</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.95</v>
+        <v>4.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>1.58</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.27</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.3</v>
+        <v>2.39</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.19</v>
+        <v>2.33</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.65</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.92</v>
+        <v>3.61</v>
       </c>
       <c r="O31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q31" t="n">
         <v>4</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="O32" t="n">
-        <v>3.24</v>
+        <v>2.37</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.38</v>
+        <v>4.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>7.4</v>
+        <v>6.55</v>
       </c>
       <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.03</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.58</v>
+        <v>2.62</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>5.11</v>
+        <v>2.66</v>
       </c>
       <c r="O33" t="n">
-        <v>2.06</v>
+        <v>3.24</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.05</v>
+        <v>3.38</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="U33" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="V33" t="n">
-        <v>5.25</v>
+        <v>7.4</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.27</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="AD33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.46</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.33</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.1</v>
+        <v>8.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.28</v>
+        <v>1.35</v>
       </c>
       <c r="O34" t="n">
-        <v>3.74</v>
+        <v>7.5</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="S34" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="T34" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="V34" t="n">
-        <v>7.2</v>
+        <v>5.95</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X34" t="n">
         <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.23</v>
+        <v>3.16</v>
       </c>
       <c r="M35" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="O35" t="n">
-        <v>2.83</v>
+        <v>3.97</v>
       </c>
       <c r="P35" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.72</v>
+        <v>2.98</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S35" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="T35" t="n">
-        <v>2.81</v>
+        <v>3.24</v>
       </c>
       <c r="U35" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.12</v>
+        <v>4.15</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
         <v>1.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="O36" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="U36" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="V36" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,55 +4824,55 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>2.93</v>
       </c>
       <c r="O37" t="n">
-        <v>2.37</v>
+        <v>3.02</v>
       </c>
       <c r="P37" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.9</v>
+        <v>3.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S37" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T37" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U37" t="n">
         <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>6.55</v>
+        <v>7.2</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X37" t="n">
         <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC37" t="n">
         <v>3.12</v>
@@ -4881,16 +4881,16 @@
         <v>1.28</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.84</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>4.37</v>
+        <v>2.26</v>
       </c>
       <c r="O38" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>2.95</v>
       </c>
       <c r="R38" t="n">
         <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T38" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="U38" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W38" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X38" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P39" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S39" t="n">
-        <v>3.15</v>
+        <v>2.53</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z39" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE39" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,65 +5177,65 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.18</v>
+        <v>1.65</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="O40" t="n">
-        <v>4.16</v>
+        <v>2.23</v>
       </c>
       <c r="P40" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.76</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="T40" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U40" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V40" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.59</v>
+        <v>3.05</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE40" t="n">
         <v>1.74</v>
@@ -5244,10 +5244,10 @@
         <v>1.95</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.26</v>
+        <v>1.96</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="M41" t="n">
-        <v>6.75</v>
+        <v>9</v>
       </c>
       <c r="N41" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="O41" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="P41" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.25</v>
+        <v>12.13</v>
       </c>
       <c r="R41" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S41" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="T41" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V41" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="W41" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="AA41" t="n">
         <v>1.28</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.26</v>
+        <v>3.55</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.88</v>
+        <v>5.7</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="M43" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="N43" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="P43" t="n">
-        <v>3.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>12.13</v>
+        <v>6.25</v>
       </c>
       <c r="R43" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>5.8</v>
+        <v>4.65</v>
       </c>
       <c r="T43" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="U43" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V43" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="AA43" t="n">
         <v>1.28</v>
       </c>
       <c r="AB43" t="n">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AH43" t="n">
-        <v>5.7</v>
+        <v>3.88</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>6.66</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.49</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>7.85</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.66</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>1.48</v>
+        <v>4.49</v>
       </c>
       <c r="O9" t="n">
-        <v>6.1</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.07</v>
+        <v>5.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AF9" t="n">
         <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N12" t="n">
         <v>4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.46</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>1.46</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>3.48</v>
       </c>
       <c r="M14" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>7.31</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>1.75</v>
+        <v>3.96</v>
       </c>
       <c r="P14" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="V14" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.9</v>
+        <v>1.27</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.48</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>4.63</v>
       </c>
       <c r="N15" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="M17" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.23</v>
+        <v>3.47</v>
       </c>
       <c r="M18" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="N18" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="T18" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="U18" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE18" t="n">
         <v>2.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46077.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.97</v>
+        <v>7.09</v>
       </c>
       <c r="M19" t="n">
-        <v>2.83</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>7.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="R19" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W19" t="n">
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46077.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>7.6</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.85</v>
+        <v>3.44</v>
       </c>
       <c r="N20" t="n">
-        <v>1.41</v>
+        <v>7.01</v>
       </c>
       <c r="O20" t="n">
-        <v>7.5</v>
+        <v>2.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.95</v>
+        <v>7.85</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="W20" t="n">
         <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AD20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.09</v>
+        <v>2.29</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46077.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>3.93</v>
       </c>
       <c r="M21" t="n">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>6.67</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
-        <v>2.2</v>
+        <v>4.87</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>1.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.84</v>
+        <v>2.34</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.23</v>
+        <v>2.59</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46077.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="M22" t="n">
         <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="O22" t="n">
-        <v>4.16</v>
+        <v>3.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.76</v>
+        <v>3.38</v>
       </c>
       <c r="R22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.35</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
         <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.87</v>
+        <v>2.28</v>
       </c>
       <c r="O23" t="n">
-        <v>2.9</v>
+        <v>3.74</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U23" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>3.65</v>
       </c>
       <c r="M24" t="n">
         <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC24" t="n">
         <v>3.1</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.26</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.74</v>
+        <v>2.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="T25" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.34</v>
+        <v>1.96</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>2.37</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>4.37</v>
+        <v>2.93</v>
       </c>
       <c r="O26" t="n">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T26" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="M27" t="n">
         <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
         <v>7.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
         <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>5.5</v>
+        <v>2.26</v>
       </c>
       <c r="O28" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>2.95</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
         <v>5.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.85</v>
+        <v>3.12</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.12</v>
+        <v>1.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.23</v>
+        <v>3.11</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>2.83</v>
+        <v>4.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.72</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
         <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="M30" t="n">
-        <v>4.3</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>5.11</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.06</v>
+        <v>2.83</v>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.05</v>
+        <v>3.72</v>
       </c>
       <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.28</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>8.75</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.61</v>
+        <v>1.35</v>
       </c>
       <c r="O31" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z31" t="n">
         <v>4</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.18</v>
-      </c>
       <c r="AA31" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>4.3</v>
+        <v>5.11</v>
       </c>
       <c r="O32" t="n">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="P32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF32" t="n">
         <v>2.11</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="O33" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE33" t="n">
+      <c r="AF33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.46</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4463,77 +4463,77 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8.75</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>1.35</v>
+        <v>3.61</v>
       </c>
       <c r="O34" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
-        <v>5.95</v>
+        <v>7.6</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.5</v>
+        <v>3.38</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N35" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3.97</v>
+        <v>3.3</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T35" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
         <v>1.02</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG35" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="M36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3.35</v>
       </c>
-      <c r="N36" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.45</v>
-      </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T36" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH36" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.93</v>
+        <v>4.37</v>
       </c>
       <c r="O37" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T37" t="n">
         <v>3.02</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.81</v>
-      </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="AD37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N38" t="n">
-        <v>2.26</v>
+        <v>5.5</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="T38" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U38" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V38" t="n">
         <v>5.8</v>
       </c>
       <c r="W38" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.12</v>
+        <v>3.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="M39" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="P39" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U39" t="n">
         <v>1.38</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.31</v>
-      </c>
       <c r="V39" t="n">
-        <v>7.8</v>
+        <v>6.55</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="AA39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5177,77 +5177,77 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.65</v>
+        <v>3.16</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>2.36</v>
       </c>
       <c r="O40" t="n">
-        <v>2.23</v>
+        <v>3.97</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="R40" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S40" t="n">
-        <v>2.87</v>
+        <v>2.47</v>
       </c>
       <c r="T40" t="n">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W40" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X40" t="n">
         <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.05</v>
+        <v>4.15</v>
       </c>
       <c r="AD40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.96</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.86</v>
+        <v>3.96</v>
       </c>
       <c r="N42" t="n">
-        <v>4.8</v>
+        <v>4.28</v>
       </c>
       <c r="O42" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="P42" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S42" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="T42" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U42" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V42" t="n">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="W42" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AC42" t="n">
         <v>2.62</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AF42" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="N44" t="n">
-        <v>4.28</v>
+        <v>4.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="P44" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z44" t="n">
         <v>4</v>
       </c>
-      <c r="R44" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V44" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AC44" t="n">
         <v>2.62</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="M45" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="P45" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="R45" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S45" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U45" t="n">
         <v>1.4</v>
       </c>
       <c r="V45" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.97</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>2</v>
       </c>
       <c r="AF45" t="n">
         <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O47" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P47" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T47" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U47" t="n">
         <v>1.4</v>
       </c>
       <c r="V47" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W47" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF47" t="n">
         <v>1.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>1.46</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.8</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="N13" t="n">
-        <v>1.46</v>
+        <v>7.31</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.48</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>4.63</v>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>4.63</v>
+        <v>3.96</v>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>3.48</v>
       </c>
       <c r="M17" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>7.31</v>
+        <v>1.73</v>
       </c>
       <c r="O17" t="n">
-        <v>1.75</v>
+        <v>3.96</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.9</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.47</v>
+        <v>7.09</v>
       </c>
       <c r="M18" t="n">
-        <v>2.61</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>4.38</v>
+        <v>7.7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.28</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>13</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.03</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.83</v>
+        <v>2.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF18" t="n">
         <v>1.54</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46077.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>7.09</v>
+        <v>3.47</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>2.61</v>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="O19" t="n">
-        <v>7.7</v>
+        <v>4.38</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.05</v>
+        <v>3.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="T19" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="V19" t="n">
-        <v>8.300000000000001</v>
+        <v>13</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.24</v>
+        <v>2.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
         <v>1.54</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46077.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="O22" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.38</v>
+        <v>2.95</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.35</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.65</v>
+        <v>8.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="O24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AA24" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>2.23</v>
+        <v>2.83</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.37</v>
+        <v>1.58</v>
       </c>
       <c r="M26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
         <v>3.3</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.77</v>
-      </c>
       <c r="T26" t="n">
-        <v>2.81</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>7.2</v>
+        <v>5.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.86</v>
+        <v>2.27</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.12</v>
+        <v>2.39</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.18</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
-        <v>4.16</v>
+        <v>2.12</v>
       </c>
       <c r="P27" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.76</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.59</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>2.12</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,49 +3753,49 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2.26</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.75</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.55</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="AA28" t="n">
         <v>1.95</v>
@@ -3804,22 +3804,22 @@
         <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="M29" t="n">
         <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="O29" t="n">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
         <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
         <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,22 +3991,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>3.61</v>
       </c>
       <c r="O30" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
         <v>1.4</v>
@@ -4015,19 +4015,19 @@
         <v>2.73</v>
       </c>
       <c r="T30" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
         <v>1.27</v>
@@ -4036,28 +4036,28 @@
         <v>3.18</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,77 +4106,77 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>8.75</v>
+        <v>2.37</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.35</v>
+        <v>2.93</v>
       </c>
       <c r="O31" t="n">
-        <v>7.5</v>
+        <v>3.02</v>
       </c>
       <c r="P31" t="n">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>3.56</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>5.95</v>
+        <v>7.2</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
         <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z31" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="M32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N32" t="n">
         <v>4.3</v>
       </c>
-      <c r="N32" t="n">
-        <v>5.11</v>
-      </c>
       <c r="O32" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.28</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.88</v>
+        <v>3.11</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2.5</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U33" t="n">
         <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
         <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.77</v>
+        <v>1.19</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O34" t="n">
         <v>3.3</v>
       </c>
-      <c r="N34" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.36</v>
       </c>
-      <c r="V34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="O35" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P35" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="R35" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S35" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="U35" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V35" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
         <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD35" t="n">
         <v>1.23</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N36" t="n">
         <v>2.36</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.87</v>
-      </c>
       <c r="O36" t="n">
-        <v>2.9</v>
+        <v>3.97</v>
       </c>
       <c r="P36" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S36" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="T36" t="n">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="U36" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W36" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.58</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,77 +4820,77 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>4.37</v>
+        <v>5</v>
       </c>
       <c r="O37" t="n">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="P37" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="R37" t="n">
         <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="T37" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="U37" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V37" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X37" t="n">
         <v>1.02</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC37" t="n">
         <v>3.05</v>
       </c>
-      <c r="AA37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE37" t="n">
         <v>1.74</v>
       </c>
-      <c r="AC37" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4939,77 +4939,77 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="M38" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>5.5</v>
+        <v>4.37</v>
       </c>
       <c r="O38" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
         <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z38" t="n">
         <v>3.05</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V38" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AA38" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>4.3</v>
+        <v>2.87</v>
       </c>
       <c r="O39" t="n">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="P39" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="T39" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.18</v>
+        <v>3.62</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.16</v>
+        <v>3.65</v>
       </c>
       <c r="M40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V40" t="n">
+        <v>6</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC40" t="n">
         <v>3.1</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>4.15</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="M41" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="N41" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="P41" t="n">
-        <v>3.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>12.13</v>
+        <v>6.25</v>
       </c>
       <c r="R41" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>5.8</v>
+        <v>4.65</v>
       </c>
       <c r="T41" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="U41" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V41" t="n">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="W41" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z41" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="AA41" t="n">
         <v>1.28</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AH41" t="n">
-        <v>5.7</v>
+        <v>3.88</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M42" t="n">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="N42" t="n">
-        <v>4.28</v>
+        <v>4.8</v>
       </c>
       <c r="O42" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="P42" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z42" t="n">
         <v>4</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V42" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AA42" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AC42" t="n">
         <v>2.62</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="M43" t="n">
-        <v>6.75</v>
+        <v>9</v>
       </c>
       <c r="N43" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="O43" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="P43" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.25</v>
+        <v>12.13</v>
       </c>
       <c r="R43" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S43" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="T43" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U43" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V43" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="W43" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="AA43" t="n">
         <v>1.28</v>
       </c>
       <c r="AB43" t="n">
-        <v>3.26</v>
+        <v>3.55</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.88</v>
+        <v>5.7</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3.86</v>
+        <v>3.96</v>
       </c>
       <c r="N44" t="n">
-        <v>4.8</v>
+        <v>4.28</v>
       </c>
       <c r="O44" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="T44" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U44" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="V44" t="n">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="W44" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AC44" t="n">
         <v>2.62</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M45" t="n">
         <v>4</v>
@@ -5785,64 +5785,64 @@
         <v>6</v>
       </c>
       <c r="O45" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="P45" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="R45" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="T45" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U45" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V45" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
         <v>4</v>
@@ -5904,64 +5904,64 @@
         <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="R46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.4</v>
       </c>
-      <c r="S46" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V46" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W46" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z46" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD46" t="n">
+      <c r="AE46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG46" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE46" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH46" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6.66</v>
+        <v>1.88</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>4.49</v>
       </c>
       <c r="O8" t="n">
-        <v>7.85</v>
+        <v>2.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>5.73</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC8" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.88</v>
+        <v>6.66</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4.49</v>
+        <v>1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>7.85</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.73</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AC9" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.8</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="N12" t="n">
-        <v>1.46</v>
+        <v>7.31</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46077.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>3.48</v>
       </c>
       <c r="M13" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>7.31</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
-        <v>1.75</v>
+        <v>3.96</v>
       </c>
       <c r="P13" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="V13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.9</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>4.63</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.96</v>
+        <v>4.63</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.75</v>
+        <v>1.46</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.48</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="N17" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7.09</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>7.01</v>
       </c>
       <c r="O18" t="n">
-        <v>7.7</v>
+        <v>2.16</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>7.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.15</v>
+        <v>3.38</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.04</v>
+        <v>2.29</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46077.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.47</v>
+        <v>7.09</v>
       </c>
       <c r="M19" t="n">
-        <v>2.61</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.42</v>
+        <v>1.44</v>
       </c>
       <c r="O19" t="n">
-        <v>4.38</v>
+        <v>7.7</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.28</v>
+        <v>2.05</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="T19" t="n">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>13</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.03</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.83</v>
+        <v>2.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF19" t="n">
         <v>1.54</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46077.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>3.47</v>
       </c>
       <c r="M20" t="n">
-        <v>3.44</v>
+        <v>2.61</v>
       </c>
       <c r="N20" t="n">
-        <v>7.01</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>2.16</v>
+        <v>4.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.85</v>
+        <v>3.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.44</v>
+        <v>2.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.29</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46077.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>2.26</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.95</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>5.8</v>
+        <v>6.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC22" t="n">
         <v>3.12</v>
       </c>
-      <c r="AA22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>3.74</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
         <v>1.85</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>8.75</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>7.5</v>
+        <v>2.23</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,28 +3396,28 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="M25" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="O25" t="n">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="P25" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
         <v>2.81</v>
@@ -3426,25 +3426,25 @@
         <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC25" t="n">
         <v>3.12</v>
@@ -3453,16 +3453,16 @@
         <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.58</v>
-      </c>
-      <c r="M26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.33</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,77 +3630,77 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>3.61</v>
       </c>
       <c r="O27" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U27" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="W27" t="n">
         <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,77 +3749,77 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.88</v>
+        <v>8.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>1.35</v>
       </c>
       <c r="O28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.5</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>6.9</v>
+        <v>5.95</v>
       </c>
       <c r="W28" t="n">
         <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.2</v>
       </c>
-      <c r="O29" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.19</v>
-      </c>
       <c r="Q29" t="n">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AA29" t="n">
         <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46077.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AB30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.79</v>
       </c>
-      <c r="AC30" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="M31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O31" t="n">
         <v>3.3</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T31" t="n">
         <v>3.02</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.81</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V31" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.38</v>
+        <v>3.07</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.12</v>
+        <v>3.68</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N32" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>2.37</v>
+        <v>2.83</v>
       </c>
       <c r="P32" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="R32" t="n">
         <v>1.4</v>
@@ -4253,19 +4253,19 @@
         <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U32" t="n">
         <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
         <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
         <v>1.27</v>
@@ -4286,16 +4286,16 @@
         <v>1.28</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,77 +4344,77 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.11</v>
+        <v>1.57</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
       <c r="O33" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="P33" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T33" t="n">
-        <v>3.02</v>
+        <v>2.45</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W33" t="n">
         <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.19</v>
+        <v>2.12</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
-        <v>3.3</v>
+        <v>4.16</v>
       </c>
       <c r="P34" t="n">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="R34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U34" t="n">
         <v>1.38</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.31</v>
-      </c>
       <c r="V34" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="AA34" t="n">
         <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.68</v>
+        <v>3.59</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="O35" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.24</v>
       </c>
-      <c r="P35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.94</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X35" t="n">
         <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AG35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.46</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.16</v>
+        <v>1.58</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N36" t="n">
-        <v>2.36</v>
+        <v>5.11</v>
       </c>
       <c r="O36" t="n">
-        <v>3.97</v>
+        <v>2.06</v>
       </c>
       <c r="P36" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.98</v>
+        <v>5.05</v>
       </c>
       <c r="R36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V36" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1.46</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V36" t="n">
-        <v>8</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AE36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.32</v>
+        <v>2.33</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4820,32 +4820,32 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.65</v>
+        <v>3.65</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="O37" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="T37" t="n">
         <v>2.6</v>
@@ -4860,37 +4860,37 @@
         <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.96</v>
+        <v>1.22</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46077.69791666666</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,43 +4943,43 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>4.37</v>
+        <v>2.66</v>
       </c>
       <c r="O38" t="n">
-        <v>2.41</v>
+        <v>3.24</v>
       </c>
       <c r="P38" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S38" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T38" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="U38" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V38" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X38" t="n">
         <v>1.02</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.07</v>
       </c>
       <c r="Y38" t="n">
         <v>1.29</v>
@@ -4988,28 +4988,28 @@
         <v>3.05</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.36</v>
+        <v>3.11</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.87</v>
+        <v>1.95</v>
       </c>
       <c r="O39" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="P39" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S39" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U39" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.62</v>
+        <v>2.95</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
         <v>3.3</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="P40" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="R40" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S40" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T40" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="U40" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V40" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="W40" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46077.69791666666</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="M41" t="n">
-        <v>6.75</v>
+        <v>9</v>
       </c>
       <c r="N41" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="O41" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="P41" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.25</v>
+        <v>12.13</v>
       </c>
       <c r="R41" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S41" t="n">
-        <v>4.65</v>
+        <v>5.8</v>
       </c>
       <c r="T41" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="V41" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="W41" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="AA41" t="n">
         <v>1.28</v>
       </c>
       <c r="AB41" t="n">
-        <v>3.26</v>
+        <v>3.55</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AH41" t="n">
-        <v>3.88</v>
+        <v>5.7</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>9</v>
+        <v>3.96</v>
       </c>
       <c r="N43" t="n">
-        <v>13</v>
+        <v>4.28</v>
       </c>
       <c r="O43" t="n">
-        <v>1.41</v>
+        <v>2.29</v>
       </c>
       <c r="P43" t="n">
-        <v>3.94</v>
+        <v>2.35</v>
       </c>
       <c r="Q43" t="n">
-        <v>12.13</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W43" t="n">
         <v>1.12</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V43" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.3</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.28</v>
       </c>
-      <c r="AB43" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD43" t="n">
+      <c r="AH43" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>5.7</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="M44" t="n">
-        <v>3.96</v>
+        <v>6.75</v>
       </c>
       <c r="N44" t="n">
-        <v>4.28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="P44" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="R44" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>3.36</v>
+        <v>4.65</v>
       </c>
       <c r="T44" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="U44" t="n">
-        <v>1.56</v>
+        <v>1.96</v>
       </c>
       <c r="V44" t="n">
-        <v>5.45</v>
+        <v>3.6</v>
       </c>
       <c r="W44" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.23</v>
+        <v>3.26</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.1</v>
+        <v>3.88</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46077.70833333334</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5772,77 +5772,77 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O45" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="P45" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="R45" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U45" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.37</v>
       </c>
       <c r="V45" t="n">
         <v>6.75</v>
       </c>
       <c r="W45" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
         <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.33</v>
+        <v>2.84</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46077.875</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5891,11 +5891,11 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M46" t="n">
         <v>4</v>
@@ -5904,64 +5904,64 @@
         <v>6</v>
       </c>
       <c r="O46" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="P46" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="T46" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U46" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V46" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH46" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46077.875</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6010,77 +6010,77 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O47" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="P47" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="R47" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S47" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U47" t="n">
         <v>1.4</v>
       </c>
       <c r="V47" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1.97</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>2</v>
       </c>
       <c r="AF47" t="n">
         <v>1.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46077.875</v>

--- a/jogos_2026-02-24.xlsx
+++ b/jogos_2026-02-24.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8.539999999999999</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46077.33333333334</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46077.33333333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>6.66</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4.49</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>2.55</v>
+        <v>7.85</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.73</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AC8" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46077.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.66</v>
+        <v>1.88</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>1.48</v>
+        <v>4.49</v>
       </c>
       <c r="O9" t="n">
-        <v>7.85</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>5.73</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AC9" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46077.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.63</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46077.66666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>4.63</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q15" t="n">
-     